--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1185,164 +1185,196 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Technician time charged, February</t>
+        </is>
+      </c>
+      <c r="B75" s="8">
+        <f>Workings!B315</f>
+        <v/>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>69.1% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Materials charged, February</t>
+        </is>
+      </c>
+      <c r="B76" s="8">
+        <f>Workings!B327</f>
+        <v/>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>$7,020 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, February 2026</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (6)</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>Workings!B314</f>
-        <v/>
-      </c>
-      <c r="C78" s="11">
-        <f>Workings!B313</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (6)</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>Workings!B325</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>Workings!B324</f>
-        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2-hour call-outs (15)</t>
+          <t>1-hour call-outs (6)</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B336</f>
+        <f>Workings!B340</f>
         <v/>
       </c>
       <c r="C80" s="11">
-        <f>Workings!B335</f>
+        <f>Workings!B339</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (4)</t>
+          <t>1.5-hour call-outs (6)</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B347</f>
+        <f>Workings!B353</f>
         <v/>
       </c>
       <c r="C81" s="11">
-        <f>Workings!B346</f>
+        <f>Workings!B352</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3-hour call-outs (18)</t>
+          <t>2-hour call-outs (15)</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B358</f>
+        <f>Workings!B366</f>
         <v/>
       </c>
       <c r="C82" s="11">
-        <f>Workings!B357</f>
+        <f>Workings!B365</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>2.5-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B83" s="8">
+        <f>Workings!B379</f>
+        <v/>
+      </c>
+      <c r="C83" s="11">
+        <f>Workings!B378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (18)</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B392</f>
+        <v/>
+      </c>
+      <c r="C84" s="11">
+        <f>Workings!B391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>4-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B83" s="8">
-        <f>Workings!B369</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B368</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="B85" s="8">
+        <f>Workings!B405</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B404</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="45" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>57 call-outs in February made a 43.8% job gross margin between them. Gross margins run from 37.0% to 47.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>57 call-outs in February billed $20,446 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 43.8% job gross margin between them. Gross margins run from 37.0% to 47.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Call-outs: 43.8% gross margin, 16.1 points clear of the 27.7% overheads need.</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
@@ -1350,10 +1382,10 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A89:D89"/>
     <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A88:D88"/>
     <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A86:D86"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
   </mergeCells>
@@ -1382,7 +1414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C372"/>
+  <dimension ref="A1:C408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -3920,14 +3952,14 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>1-hour call-outs (6)</t>
+          <t>Call-out revenue, February</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="12" t="inlineStr">
         <is>
-          <t>Call-outs of this length in February, added together</t>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -3942,498 +3974,818 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B309" s="13" t="n">
-        <v>6</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B310" s="13" t="n">
-        <v>1871</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B311" s="13" t="n">
-        <v>-770</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B311" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B312" s="13" t="n">
-        <v>-408</v>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B312" s="13">
+        <f>B310*(1+B311)</f>
+        <v/>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B313" s="13">
-        <f>B310+B311+B312</f>
-        <v/>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B313" s="13" t="n">
+        <v>9126</v>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B314" s="16">
-        <f>B313/B310</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315"/>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B314" s="13">
+        <f>B309+B313</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B315" s="16">
+        <f>B309/B314</f>
+        <v/>
+      </c>
+    </row>
     <row r="316"/>
-    <row r="317">
-      <c r="A317" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (6)</t>
-        </is>
-      </c>
-    </row>
+    <row r="317"/>
     <row r="318">
-      <c r="A318" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
+      <c r="A318" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, February</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="6" t="inlineStr"/>
-      <c r="B319" s="7" t="inlineStr">
+      <c r="A319" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="6" t="inlineStr"/>
+      <c r="B320" s="7" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B320" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B321" s="13" t="n">
-        <v>2554</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>-960</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B323" s="13" t="n">
-        <v>-612</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B323" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
       <c r="B324" s="13">
-        <f>B321+B322+B323</f>
+        <f>B322*(1+B323)</f>
         <v/>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B325" s="16">
-        <f>B324/B321</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328">
-      <c r="A328" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="12" t="inlineStr">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B325" s="13" t="n">
+        <v>9126</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B326" s="13">
+        <f>B321+B325</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B327" s="16">
+        <f>B321/B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330">
+      <c r="A330" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" s="6" t="inlineStr"/>
-      <c r="B330" s="7" t="inlineStr">
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr"/>
+      <c r="B332" s="7" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B331" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B332" s="13" t="n">
-        <v>7184</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Call-outs</t>
         </is>
       </c>
       <c r="B333" s="13" t="n">
-        <v>-2180</v>
+        <v>6</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B334" s="13" t="n">
-        <v>-2040</v>
+        <v>870</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B335" s="13" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B336" s="13">
+        <f>B334+B335</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B337" s="13" t="n">
+        <v>-770</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B335" s="13">
-        <f>B332+B333+B334</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="15" t="inlineStr">
+      <c r="B339" s="13">
+        <f>B336+B337+B338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B336" s="16">
-        <f>B335/B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339">
-      <c r="A339" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="12" t="inlineStr">
+      <c r="B340" s="16">
+        <f>B339/B336</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" s="6" t="inlineStr"/>
-      <c r="B341" s="7" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr"/>
+      <c r="B345" s="7" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B342" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B343" s="13" t="n">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B344" s="13" t="n">
-        <v>-460</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B345" s="13" t="n">
-        <v>-680</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B346" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B347" s="13" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B349" s="13">
+        <f>B347+B348</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="n">
+        <v>-960</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B351" s="13" t="n">
+        <v>-612</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B346" s="13">
-        <f>B343+B344+B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="15" t="inlineStr">
+      <c r="B352" s="13">
+        <f>B349+B350+B351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B347" s="16">
-        <f>B346/B343</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350">
-      <c r="A350" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="12" t="inlineStr">
+      <c r="B353" s="16">
+        <f>B352/B349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" s="6" t="inlineStr"/>
-      <c r="B352" s="7" t="inlineStr">
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr"/>
+      <c r="B358" s="7" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="B359" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="n">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B354" s="13" t="n">
-        <v>10287</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B355" s="13" t="n">
-        <v>-1890</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B356" s="13" t="n">
-        <v>-3672</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B357" s="13">
-        <f>B354+B355+B356</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B358" s="16">
-        <f>B357/B354</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361">
-      <c r="A361" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
+      <c r="B362" s="13">
+        <f>B360+B361</f>
+        <v/>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="6" t="inlineStr"/>
-      <c r="B363" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="n">
+        <v>-2180</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time at cost</t>
         </is>
       </c>
       <c r="B364" s="13" t="n">
-        <v>8</v>
+        <v>-2040</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B365" s="13">
+        <f>B362+B363+B364</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B366" s="16">
+        <f>B365/B362</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr"/>
+      <c r="B371" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B372" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B373" s="13" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B365" s="13" t="n">
-        <v>5628</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B366" s="13" t="n">
+      <c r="B375" s="13">
+        <f>B373+B374</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="n">
+        <v>-460</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B377" s="13" t="n">
+        <v>-680</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B378" s="13">
+        <f>B375+B376+B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B379" s="16">
+        <f>B378/B375</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr"/>
+      <c r="B384" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B385" s="13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="n">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B388" s="13">
+        <f>B386+B387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B389" s="13" t="n">
+        <v>-1890</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="n">
+        <v>-3672</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B391" s="13">
+        <f>B388+B389+B390</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B392" s="16">
+        <f>B391/B388</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr"/>
+      <c r="B397" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B398" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="n">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B401" s="13">
+        <f>B399+B400</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="n">
         <v>-760</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
+      <c r="B403" s="13" t="n">
         <v>-2176</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B368" s="13">
-        <f>B365+B366+B367</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" s="15" t="inlineStr">
+      <c r="B404" s="13">
+        <f>B401+B402+B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B369" s="16">
-        <f>B368/B365</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
+      <c r="B405" s="16">
+        <f>B404/B401</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4446,7 +4798,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="14" manualBreakCount="14">
+  <rowBreaks count="15" manualBreakCount="15">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="57" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
@@ -4459,8 +4811,9 @@
     <brk id="257" min="0" max="16383" man="1"/>
     <brk id="283" min="0" max="16383" man="1"/>
     <brk id="305" min="0" max="16383" man="1"/>
-    <brk id="327" min="0" max="16383" man="1"/>
-    <brk id="349" min="0" max="16383" man="1"/>
+    <brk id="329" min="0" max="16383" man="1"/>
+    <brk id="355" min="0" max="16383" man="1"/>
+    <brk id="381" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -25,48 +25,58 @@
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -99,36 +109,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1393,8 +1403,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4791,8 +4801,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7008,8 +7018,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Before overheads, so this is not profit. Pick a type of job and every number, chart and note on the page follows it.</t>
+          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
@@ -615,232 +615,236 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>January 35.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Job gross margin, January · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, February 2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Workings!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B46</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>Workings!B45</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B55</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="8">
+        <f>Workings!B81</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>In February maintenance contracts made a 59.6% job gross margin, installations made a 31.2% job gross margin, call-outs and repairs made a 43.8% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 27.7% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: 59.6% gross margin, the most profitable work you do. Every type of job clears it; installations only just.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Installations: 31.2% gross margin, 3.8 points under the 35.0% target: about $4,851 on $129,300 of revenue in February. Maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Job gross margin, February · Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>January 59.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, February 2026</t>
+      <c r="B33" s="8">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Job gross margin, January · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Carindale vet clinic</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>Workings!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C36" s="11">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
-        <f>Workings!B103</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>Workings!B102</f>
-        <v/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, February 2026</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
-        <f>Workings!B116</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>Workings!B115</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -855,7 +859,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B40" s="8">
@@ -870,7 +874,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -885,7 +889,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B42" s="8">
@@ -900,7 +904,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -915,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B44" s="8">
@@ -930,7 +934,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -945,7 +949,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -960,7 +964,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -972,432 +976,556 @@
         <v/>
       </c>
     </row>
-    <row r="48"/>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B48" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C48" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>All 13 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>The Kangaroo Point townhouses contract: 58.2% gross margin, 30.5 points clear of the 27.7% overheads need. Maintenance contracts overall: 59.6% gross margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Installations</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>Workings!B242</f>
-        <v/>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>January 23.9%</t>
+    <row r="57" ht="45" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in February). All maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
         </is>
       </c>
     </row>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in February 2026</t>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Taringa warehouse EV chargers</t>
+          <t>Job gross margin, February · Installations</t>
         </is>
       </c>
       <c r="B61" s="8">
-        <f>Workings!B255</f>
-        <v/>
-      </c>
-      <c r="C61" s="11">
-        <f>Workings!B254</f>
-        <v/>
+        <f>Workings!B294</f>
+        <v/>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Taringa clinic LED lighting</t>
+          <t>Job gross margin, January · Installations</t>
         </is>
       </c>
       <c r="B62" s="8">
-        <f>Workings!B268</f>
-        <v/>
-      </c>
-      <c r="C62" s="11">
-        <f>Workings!B267</f>
-        <v/>
+        <f>Workings!B303</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B63" s="8">
+        <f>Workings!B319</f>
+        <v/>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in February 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Taringa warehouse EV chargers</t>
+        </is>
+      </c>
+      <c r="B67" s="8">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C67" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Taringa clinic LED lighting</t>
+        </is>
+      </c>
+      <c r="B68" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>Kedron shop switchboard upgrade</t>
         </is>
       </c>
-      <c r="B63" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C63" s="11">
-        <f>Workings!B280</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B69" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Salisbury gym air-con install</t>
         </is>
       </c>
-      <c r="B64" s="8">
-        <f>Workings!B294</f>
-        <v/>
-      </c>
-      <c r="C64" s="11">
-        <f>Workings!B293</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>3 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 22.9% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $18,100 job. Jobs need 27.7% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Below the 27.7% overheads need: Kedron shop switchboard upgrade (24.1%), Salisbury gym air-con install (22.9%). Most profitable: Taringa warehouse EV chargers (40.5%).</t>
-        </is>
+      <c r="B70" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>Workings!B371</f>
+        <v/>
       </c>
     </row>
     <row r="71"/>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B74" s="8">
-        <f>Workings!B303</f>
-        <v/>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>January 43.3%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>3 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 22.9% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $18,100 job. Jobs need 27.7% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time charged, February</t>
-        </is>
-      </c>
-      <c r="B75" s="8">
-        <f>Workings!B315</f>
-        <v/>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>69.1% of call-out revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Materials charged, February</t>
-        </is>
-      </c>
-      <c r="B76" s="8">
-        <f>Workings!B327</f>
-        <v/>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>$7,020 at cost, plus 30%</t>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>3 installations under the 35.0% target, worth about $6,913 between them on $91,500 of revenue. The biggest gap, Kedron shop switchboard upgrade: 24.1% gross margin, 10.9 points under the 35.0% target: about $3,921 on $36,100 of revenue in February. It's below the 27.7% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
     <row r="77"/>
     <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, February 2026</t>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr"/>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1-hour call-outs (6)</t>
+          <t>Job gross margin, February · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B340</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>Workings!B339</f>
-        <v/>
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (6)</t>
+          <t>Job gross margin, January · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B353</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B352</f>
-        <v/>
+        <f>Workings!B390</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2-hour call-outs (15)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B366</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>Workings!B365</f>
-        <v/>
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (4)</t>
+          <t>Technician time charged, February</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B379</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B378</f>
-        <v/>
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>69.1% of call-out revenue</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Materials charged, February</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>$7,020 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, February 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (6)</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (15)</t>
+        </is>
+      </c>
+      <c r="B90" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B91" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>3-hour call-outs (18)</t>
         </is>
       </c>
-      <c r="B84" s="8">
-        <f>Workings!B392</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B391</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="B92" s="8">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C92" s="11">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>4-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B85" s="8">
-        <f>Workings!B405</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B404</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="B93" s="8">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C93" s="11">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>57 call-outs in February billed $20,446 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 43.8% job gross margin between them. Gross margins run from 37.0% to 47.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Call-outs: 43.8% gross margin, 16.1 points clear of the 27.7% overheads need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 43.8% gross margin, 8.8 points over the 35.0% target ($2,614 ahead on $29,572 in February).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96"/>
+    <row r="103"/>
+    <row r="104"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1410,10 +1538,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="48" min="0" max="16383" man="1"/>
-    <brk id="72" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="18" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
+    <brk id="64" min="0" max="16383" man="1"/>
+    <brk id="85" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1424,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C408"/>
+  <dimension ref="A1:C512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1690,14 +1819,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts, February</t>
+          <t>All lines: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1834,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Feb 2026</t>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1850,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>37500</v>
+        <v>196372</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>164780</v>
       </c>
     </row>
     <row r="35">
@@ -1726,7 +1863,10 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>15158</v>
+        <v>120662</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>106590</v>
       </c>
     </row>
     <row r="36">
@@ -1739,6 +1879,10 @@
         <f>B34-B35</f>
         <v/>
       </c>
+      <c r="C36" s="13">
+        <f>C34-C35</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -1748,6 +1892,10 @@
       </c>
       <c r="B37" s="16">
         <f>B36/B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>C36/C34</f>
         <v/>
       </c>
     </row>
@@ -1756,14 +1904,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Installations, February</t>
+          <t>From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -1778,407 +1926,406 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>129300</v>
+        <v>75710</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>88896</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <f>B43-B44</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>59432</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>B45/B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B46" s="13">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B43-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>59320</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs, February</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>B47-B48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>196372</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B43/B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>(B46+B48)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts, February</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>29572</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
-        <v>16608</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B54" s="13">
-        <f>B52-B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B55" s="16">
-        <f>B54/B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: gross margin, February and January</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
-        </is>
+      <c r="B60" s="13" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>37500</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>35800</v>
+        <v>15158</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>15158</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>14516</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13">
+        <f>B60-B61</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B63" s="13">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="13">
-        <f>C61-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B64" s="16">
-        <f>B63/B61</f>
-        <v/>
-      </c>
-      <c r="C64" s="16">
-        <f>C63/C61</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B63" s="16">
+        <f>B62/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Installations, February</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>129300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>1700</v>
+        <v>88896</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n">
-        <v>-30</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B71" s="13">
+        <f>B69-B70</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B72" s="16">
+        <f>B71/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>-B73*B74</f>
-        <v/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs, February</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>B70+B71+B72+B75</f>
-        <v/>
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>29572</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>16608</v>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>B78-B79</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>2200</v>
-      </c>
-    </row>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B81" s="16">
+        <f>B80/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>-40</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts: gross margin, February and January</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>0</v>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="n">
-        <v>12</v>
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>68</v>
+        <v>37500</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>-B86*B87</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>15158</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>14516</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>B83+B84+B85+B88</f>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B90" s="16">
-        <f>B89/B83</f>
+        <f>B89/B87</f>
+        <v/>
+      </c>
+      <c r="C90" s="16">
+        <f>C89/C87</f>
         <v/>
       </c>
     </row>
@@ -2187,14 +2334,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Maintenance contracts: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2349,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
         </is>
       </c>
     </row>
@@ -2213,187 +2365,200 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>1800</v>
+        <v>37500</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>35800</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>-40</v>
+        <v>15158</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>14516</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>0</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>C96-C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>-B99*B100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98/B96</f>
+        <v/>
+      </c>
+      <c r="C99" s="16">
+        <f>C98/C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>B96+B97+B98+B101</f>
-        <v/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, February 2026</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B103" s="16">
-        <f>B102/B96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>75710</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>59432</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B108" s="13">
+        <f>B106-B107</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>3600</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>B105-B108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>-80</v>
+        <v>59320</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="n">
-        <v>0</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B111" s="13">
+        <f>B109-B110</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="n">
-        <v>20</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>196372</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B113" s="14">
+        <f>B105/B112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>-B112*B113</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="14">
+        <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B115" s="13">
-        <f>B109+B110+B111+B114</f>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>(B108+B110)/B112</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>B115/B109</f>
-        <v/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="117"/>
@@ -2401,7 +2566,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2592,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>3400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="123">
@@ -2437,7 +2602,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="124">
@@ -2457,7 +2622,7 @@
         </is>
       </c>
       <c r="B125" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -2508,7 +2673,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2699,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="136">
@@ -2544,7 +2709,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="137">
@@ -2564,7 +2729,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
@@ -2615,7 +2780,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2806,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="149">
@@ -2651,7 +2816,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="150">
@@ -2671,7 +2836,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152">
@@ -2722,7 +2887,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2913,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="162">
@@ -2758,7 +2923,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="163">
@@ -2778,7 +2943,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165">
@@ -2829,7 +2994,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -2855,7 +3020,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>4200</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="175">
@@ -2865,7 +3030,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="176">
@@ -2885,7 +3050,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178">
@@ -2936,7 +3101,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -2962,7 +3127,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>2800</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="188">
@@ -2992,7 +3157,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191">
@@ -3043,7 +3208,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3234,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>2600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="201">
@@ -3079,7 +3244,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="202">
@@ -3099,7 +3264,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204">
@@ -3150,7 +3315,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3341,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>3900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="214">
@@ -3186,7 +3351,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-110</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="215">
@@ -3206,7 +3371,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -3257,7 +3422,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3448,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="227">
@@ -3293,7 +3458,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="228">
@@ -3313,7 +3478,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="230">
@@ -3364,14 +3529,14 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, February and January</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3379,12 +3544,7 @@
       <c r="A238" s="6" t="inlineStr"/>
       <c r="B238" s="7" t="inlineStr">
         <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="C238" s="7" t="inlineStr">
-        <is>
-          <t>Jan 26</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -3395,480 +3555,485 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>129300</v>
-      </c>
-      <c r="C239" s="13" t="n">
-        <v>97500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C240" s="13" t="n">
-        <v>74216</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B241" s="13">
-        <f>B239-B240</f>
-        <v/>
-      </c>
-      <c r="C241" s="13">
-        <f>C239-C240</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B242" s="16">
-        <f>B241/B239</f>
-        <v/>
-      </c>
-      <c r="C242" s="16">
-        <f>C241/C239</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243"/>
-    <row r="244"/>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B242" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B244" s="13">
+        <f>-B242*B243</f>
+        <v/>
+      </c>
+    </row>
     <row r="245">
-      <c r="A245" s="5" t="inlineStr">
-        <is>
-          <t>Taringa warehouse EV chargers</t>
-        </is>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B245" s="13">
+        <f>B239+B240+B241+B244</f>
+        <v/>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="12" t="inlineStr">
+      <c r="A246" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B246" s="16">
+        <f>B245/B239</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="6" t="inlineStr"/>
-      <c r="B247" s="7" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B248" s="13" t="n">
-        <v>37800</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B249" s="13" t="n">
-        <v>-11900</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B250" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B251" s="17" t="n">
-        <v>156</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>68</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B253" s="13">
-        <f>-B251*B252</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B253" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B257" s="13">
+        <f>-B255*B256</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B254" s="13">
-        <f>B248+B249+B250+B253</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="15" t="inlineStr">
+      <c r="B258" s="13">
+        <f>B252+B253+B254+B257</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B255" s="16">
-        <f>B254/B248</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Taringa clinic LED lighting</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="B259" s="16">
+        <f>B258/B252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr"/>
-      <c r="B260" s="7" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="n">
-        <v>37300</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="n">
-        <v>-14500</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B263" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="n">
-        <v>155</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>68</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B266" s="13">
-        <f>-B264*B265</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B269" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B270" s="13">
+        <f>-B268*B269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B267" s="13">
-        <f>B261+B262+B263+B266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
+      <c r="B271" s="13">
+        <f>B265+B266+B267+B270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B268" s="16">
-        <f>B267/B261</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Kedron shop switchboard upgrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
+      <c r="B272" s="16">
+        <f>B271/B265</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
-      <c r="B273" s="7" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B274" s="13" t="n">
-        <v>36100</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B275" s="13" t="n">
-        <v>-14300</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B276" s="13" t="n">
-        <v>-3600</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B277" s="17" t="n">
-        <v>139.5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>68</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B279" s="13">
-        <f>-B277*B278</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B279" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B280" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B281" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B282" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B283" s="13">
+        <f>-B281*B282</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B280" s="13">
-        <f>B274+B275+B276+B279</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="15" t="inlineStr">
+      <c r="B284" s="13">
+        <f>B278+B279+B280+B283</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B281" s="16">
-        <f>B280/B274</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Salisbury gym air-con install</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B287" s="13" t="n">
-        <v>18100</v>
-      </c>
-    </row>
+      <c r="B285" s="16">
+        <f>B284/B278</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286"/>
+    <row r="287"/>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B288" s="13" t="n">
-        <v>-7800</v>
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, February and January</t>
+        </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B289" s="13" t="n">
-        <v>-1300</v>
+      <c r="A289" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B290" s="17" t="n">
-        <v>71.5</v>
+      <c r="A290" s="6" t="inlineStr"/>
+      <c r="B290" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C290" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>68</v>
+        <v>129300</v>
+      </c>
+      <c r="C291" s="13" t="n">
+        <v>97500</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B292" s="13">
-        <f>-B290*B291</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="n">
+        <v>88896</v>
+      </c>
+      <c r="C292" s="13" t="n">
+        <v>74216</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B293" s="13">
-        <f>B287+B288+B289+B292</f>
+        <f>B291-B292</f>
+        <v/>
+      </c>
+      <c r="C293" s="13">
+        <f>C291-C292</f>
         <v/>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B294" s="16">
-        <f>B293/B287</f>
+        <f>B293/B291</f>
+        <v/>
+      </c>
+      <c r="C294" s="16">
+        <f>C293/C291</f>
         <v/>
       </c>
     </row>
@@ -3877,7 +4042,7 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, February and January</t>
+          <t>Installations: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -3908,10 +4073,10 @@
         </is>
       </c>
       <c r="B300" s="13" t="n">
-        <v>29572</v>
+        <v>129300</v>
       </c>
       <c r="C300" s="13" t="n">
-        <v>31480</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="301">
@@ -3921,10 +4086,10 @@
         </is>
       </c>
       <c r="B301" s="13" t="n">
-        <v>16608</v>
+        <v>88896</v>
       </c>
       <c r="C301" s="13" t="n">
-        <v>17858</v>
+        <v>74216</v>
       </c>
     </row>
     <row r="302">
@@ -3962,14 +4127,14 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>Call-out revenue, February</t>
+          <t>From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -3984,818 +4149,1710 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B309" s="13" t="n">
-        <v>20446</v>
+        <v>75710</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B310" s="13" t="n">
-        <v>7020</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B311" s="14" t="n">
-        <v>0.3</v>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B311" s="13" t="n">
+        <v>59432</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Technician time not charged to jobs</t>
         </is>
       </c>
       <c r="B312" s="13">
-        <f>B310*(1+B311)</f>
+        <f>B310-B311</f>
         <v/>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B313" s="13" t="n">
-        <v>9126</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B313" s="13">
+        <f>B309-B312</f>
+        <v/>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B314" s="13">
-        <f>B309+B313</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B314" s="13" t="n">
+        <v>59320</v>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B315" s="16">
-        <f>B309/B314</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316"/>
-    <row r="317"/>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B315" s="13">
+        <f>B313-B314</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B316" s="13" t="n">
+        <v>196372</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B317" s="14">
+        <f>B309/B316</f>
+        <v/>
+      </c>
+    </row>
     <row r="318">
-      <c r="A318" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, February</t>
-        </is>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B318" s="14">
+        <f>B315/B316</f>
+        <v/>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
+      <c r="A319" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B319" s="16">
+        <f>(B312+B314)/B316</f>
+        <v/>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="6" t="inlineStr"/>
-      <c r="B320" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B321" s="13" t="n">
-        <v>20446</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B322" s="13" t="n">
-        <v>7020</v>
-      </c>
-    </row>
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321"/>
+    <row r="322"/>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B323" s="14" t="n">
-        <v>0.3</v>
+      <c r="A323" s="5" t="inlineStr">
+        <is>
+          <t>Taringa warehouse EV chargers</t>
+        </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B324" s="13">
-        <f>B322*(1+B323)</f>
-        <v/>
+      <c r="A324" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B325" s="13" t="n">
-        <v>9126</v>
+      <c r="A325" s="6" t="inlineStr"/>
+      <c r="B325" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B326" s="13">
-        <f>B321+B325</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B326" s="13" t="n">
+        <v>37800</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B327" s="16">
-        <f>B321/B326</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328"/>
-    <row r="329"/>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B327" s="13" t="n">
+        <v>-11900</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B328" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B329" s="17" t="n">
+        <v>156</v>
+      </c>
+    </row>
     <row r="330">
-      <c r="A330" s="5" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (6)</t>
-        </is>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B330" s="13" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B331" s="13">
+        <f>-B329*B330</f>
+        <v/>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="6" t="inlineStr"/>
-      <c r="B332" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B332" s="13">
+        <f>B326+B327+B328+B331</f>
+        <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B334" s="13" t="n">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B335" s="13" t="n">
-        <v>1001</v>
-      </c>
-    </row>
+      <c r="A333" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B333" s="16">
+        <f>B332/B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334"/>
+    <row r="335"/>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B336" s="13">
-        <f>B334+B335</f>
-        <v/>
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Taringa clinic LED lighting</t>
+        </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B337" s="13" t="n">
-        <v>-770</v>
+      <c r="A337" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B338" s="13" t="n">
-        <v>-408</v>
+      <c r="A338" s="6" t="inlineStr"/>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="n">
+        <v>37300</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="n">
+        <v>-14500</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B342" s="17" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B344" s="13">
+        <f>-B342*B343</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B339" s="13">
-        <f>B336+B337+B338</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="15" t="inlineStr">
+      <c r="B345" s="13">
+        <f>B339+B340+B341+B344</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B340" s="16">
-        <f>B339/B336</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343">
-      <c r="A343" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="6" t="inlineStr"/>
-      <c r="B345" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B346" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B347" s="13" t="n">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="n">
-        <v>1248</v>
-      </c>
-    </row>
+      <c r="B346" s="16">
+        <f>B345/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347"/>
+    <row r="348"/>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B349" s="13">
-        <f>B347+B348</f>
-        <v/>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>Kedron shop switchboard upgrade</t>
+        </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="n">
-        <v>-960</v>
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="n">
-        <v>-612</v>
+      <c r="A351" s="6" t="inlineStr"/>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="n">
+        <v>36100</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="n">
+        <v>-14300</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="n">
+        <v>-3600</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B355" s="17" t="n">
+        <v>139.5</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B357" s="13">
+        <f>-B355*B356</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B352" s="13">
-        <f>B349+B350+B351</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="15" t="inlineStr">
+      <c r="B358" s="13">
+        <f>B352+B353+B354+B357</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B353" s="16">
-        <f>B352/B349</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="6" t="inlineStr"/>
-      <c r="B358" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="n">
-        <v>4350</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B361" s="13" t="n">
-        <v>2834</v>
-      </c>
-    </row>
+      <c r="B359" s="16">
+        <f>B358/B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360"/>
+    <row r="361"/>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B362" s="13">
-        <f>B360+B361</f>
-        <v/>
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>Salisbury gym air-con install</t>
+        </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B363" s="13" t="n">
-        <v>-2180</v>
+      <c r="A363" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="n">
-        <v>-2040</v>
+      <c r="A364" s="6" t="inlineStr"/>
+      <c r="B364" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="n">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="n">
+        <v>-7800</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B367" s="13" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B368" s="17" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B370" s="13">
+        <f>-B368*B369</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B365" s="13">
-        <f>B362+B363+B364</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="15" t="inlineStr">
+      <c r="B371" s="13">
+        <f>B365+B366+B367+B370</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B366" s="16">
-        <f>B365/B362</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="6" t="inlineStr"/>
-      <c r="B371" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B372" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B373" s="13" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="n">
-        <v>598</v>
-      </c>
-    </row>
+      <c r="B372" s="16">
+        <f>B371/B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373"/>
+    <row r="374"/>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B375" s="13">
-        <f>B373+B374</f>
-        <v/>
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, February and January</t>
+        </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="n">
-        <v>-460</v>
+      <c r="A376" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B377" s="13" t="n">
-        <v>-680</v>
+      <c r="A377" s="6" t="inlineStr"/>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C377" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B378" s="13">
-        <f>B375+B376+B377</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B378" s="13" t="n">
+        <v>29572</v>
+      </c>
+      <c r="C378" s="13" t="n">
+        <v>31480</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B379" s="16">
-        <f>B378/B375</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382">
-      <c r="A382" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (18)</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
-      </c>
-    </row>
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B379" s="13" t="n">
+        <v>16608</v>
+      </c>
+      <c r="C379" s="13" t="n">
+        <v>17858</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B380" s="13">
+        <f>B378-B379</f>
+        <v/>
+      </c>
+      <c r="C380" s="13">
+        <f>C378-C379</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B381" s="16">
+        <f>B380/B378</f>
+        <v/>
+      </c>
+      <c r="C381" s="16">
+        <f>C380/C378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382"/>
+    <row r="383"/>
     <row r="384">
-      <c r="A384" s="6" t="inlineStr"/>
-      <c r="B384" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
+      <c r="A384" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B385" s="13" t="n">
-        <v>18</v>
+      <c r="A385" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B386" s="13" t="n">
-        <v>7830</v>
+      <c r="A386" s="6" t="inlineStr"/>
+      <c r="B386" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="C386" s="7" t="inlineStr">
+        <is>
+          <t>Jan 26</t>
+        </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B387" s="13" t="n">
-        <v>2457</v>
+        <v>29572</v>
+      </c>
+      <c r="C387" s="13" t="n">
+        <v>31480</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B388" s="13">
-        <f>B386+B387</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B388" s="13" t="n">
+        <v>16608</v>
+      </c>
+      <c r="C388" s="13" t="n">
+        <v>17858</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B389" s="13" t="n">
-        <v>-1890</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B389" s="13">
+        <f>B387-B388</f>
+        <v/>
+      </c>
+      <c r="C389" s="13">
+        <f>C387-C388</f>
+        <v/>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B390" s="13" t="n">
-        <v>-3672</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B391" s="13">
-        <f>B388+B389+B390</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B392" s="16">
-        <f>B391/B388</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393"/>
-    <row r="394"/>
+      <c r="A390" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B390" s="16">
+        <f>B389/B387</f>
+        <v/>
+      </c>
+      <c r="C390" s="16">
+        <f>C389/C387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393">
+      <c r="A393" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, February 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
     <row r="395">
-      <c r="A395" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (8)</t>
+      <c r="A395" s="6" t="inlineStr"/>
+      <c r="B395" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in February, added together</t>
-        </is>
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B396" s="13" t="n">
+        <v>75710</v>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="6" t="inlineStr"/>
-      <c r="B397" s="7" t="inlineStr">
-        <is>
-          <t>Feb 2026</t>
-        </is>
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B397" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
       <c r="B398" s="13" t="n">
-        <v>8</v>
+        <v>59432</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B399" s="13" t="n">
-        <v>4640</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B399" s="13">
+        <f>B397-B398</f>
+        <v/>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B400" s="13" t="n">
-        <v>988</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B400" s="13">
+        <f>B396-B399</f>
+        <v/>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B401" s="13">
-        <f>B399+B400</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B401" s="13" t="n">
+        <v>59320</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B402" s="13" t="n">
-        <v>-760</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B402" s="13">
+        <f>B400-B401</f>
+        <v/>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B403" s="13" t="n">
-        <v>-2176</v>
+        <v>196372</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B404" s="14">
+        <f>B396/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B405" s="14">
+        <f>B402/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B406" s="16">
+        <f>(B399+B401)/B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410">
+      <c r="A410" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, February</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr"/>
+      <c r="B412" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="n">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B414" s="13" t="n">
+        <v>7020</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B415" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B416" s="13">
+        <f>B414*(1+B415)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B417" s="13" t="n">
+        <v>9126</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B418" s="13">
+        <f>B413+B417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B419" s="16">
+        <f>B413/B418</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422">
+      <c r="A422" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, February</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr"/>
+      <c r="B424" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="n">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B426" s="13" t="n">
+        <v>7020</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B427" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B428" s="13">
+        <f>B426*(1+B427)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B429" s="13" t="n">
+        <v>9126</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B430" s="13">
+        <f>B425+B429</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B431" s="16">
+        <f>B425/B430</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr"/>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B437" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B438" s="13" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B439" s="13" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B440" s="13">
+        <f>B438+B439</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B441" s="13" t="n">
+        <v>-770</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B404" s="13">
-        <f>B401+B402+B403</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="15" t="inlineStr">
+      <c r="B443" s="13">
+        <f>B440+B441+B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B405" s="16">
-        <f>B404/B401</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
+      <c r="B444" s="16">
+        <f>B443/B440</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr"/>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B450" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B451" s="13" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B453" s="13">
+        <f>B451+B452</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B454" s="13" t="n">
+        <v>-960</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B455" s="13" t="n">
+        <v>-612</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B456" s="13">
+        <f>B453+B454+B455</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B457" s="16">
+        <f>B456/B453</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr"/>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B463" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B464" s="13" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B465" s="13" t="n">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B466" s="13">
+        <f>B464+B465</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B467" s="13" t="n">
+        <v>-2180</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B468" s="13" t="n">
+        <v>-2040</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B469" s="13">
+        <f>B466+B467+B468</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B470" s="16">
+        <f>B469/B466</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr"/>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B476" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B477" s="13" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B478" s="13" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B479" s="13">
+        <f>B477+B478</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="n">
+        <v>-460</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="n">
+        <v>-680</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B482" s="13">
+        <f>B479+B480+B481</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B483" s="16">
+        <f>B482/B479</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr"/>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B489" s="13" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B490" s="13" t="n">
+        <v>7830</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B491" s="13" t="n">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B492" s="13">
+        <f>B490+B491</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B493" s="13" t="n">
+        <v>-1890</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B494" s="13" t="n">
+        <v>-3672</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B495" s="13">
+        <f>B492+B493+B494</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B496" s="16">
+        <f>B495/B492</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in February, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr"/>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B502" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B503" s="13" t="n">
+        <v>4640</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B504" s="13" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B505" s="13">
+        <f>B503+B504</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B506" s="13" t="n">
+        <v>-760</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B507" s="13" t="n">
+        <v>-2176</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B508" s="13">
+        <f>B505+B506+B507</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B509" s="16">
+        <f>B508/B505</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4808,22 +5865,26 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="15" manualBreakCount="15">
+  <rowBreaks count="19" manualBreakCount="19">
     <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="57" min="0" max="16383" man="1"/>
-    <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="105" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
     <brk id="131" min="0" max="16383" man="1"/>
     <brk id="157" min="0" max="16383" man="1"/>
     <brk id="183" min="0" max="16383" man="1"/>
     <brk id="209" min="0" max="16383" man="1"/>
     <brk id="235" min="0" max="16383" man="1"/>
-    <brk id="257" min="0" max="16383" man="1"/>
-    <brk id="283" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="287" min="0" max="16383" man="1"/>
     <brk id="305" min="0" max="16383" man="1"/>
-    <brk id="329" min="0" max="16383" man="1"/>
-    <brk id="355" min="0" max="16383" man="1"/>
-    <brk id="381" min="0" max="16383" man="1"/>
+    <brk id="335" min="0" max="16383" man="1"/>
+    <brk id="361" min="0" max="16383" man="1"/>
+    <brk id="392" min="0" max="16383" man="1"/>
+    <brk id="421" min="0" max="16383" man="1"/>
+    <brk id="446" min="0" max="16383" man="1"/>
+    <brk id="472" min="0" max="16383" man="1"/>
+    <brk id="498" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -12,7 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Job_gross_margin_February_All_jobs">'Report'!$B$15</definedName>
+    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
+    <definedName name="Job_gross_margin_February_Maintenance_contracts">'Report'!$B$41</definedName>
+    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
+    <definedName name="Job_gross_margin_February_Installations">'Report'!$B$79</definedName>
+    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$80</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$81</definedName>
+    <definedName name="Job_gross_margin_February_Call_outs_and_repairs">'Report'!$B$105</definedName>
+    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$106</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$107</definedName>
+    <definedName name="Technician_time_charged_February">'Report'!$B$108</definedName>
+    <definedName name="Materials_charged_February">'Report'!$B$109</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$134</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,11 +67,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -70,6 +82,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,27 +135,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +238,834 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin by type of job, February 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$21:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each maintenance contract, February 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$47:$A$59</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$47:$B$59</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each installation invoiced in February 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$85:$A$88</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$85:$B$88</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on call-outs by length, February 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$113:$A$118</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$113:$B$118</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$23:$D$39</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$40:$D$56</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$57:$D$73</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="4230000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>83</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>111</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="job_margins_Data" displayName="job_margins_Data" ref="A5:G73" headerRowCount="1">
+  <autoFilter ref="A5:G73"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -529,14 +1376,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -552,14 +1399,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>February's jobs made $75,710 gross margin (38.6%). Technician time not charged to jobs took ($4,832) and overheads $59,320, leaving $21,222 profit before tax (10.8% of revenue). To cover overheads, jobs need a 27.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -567,14 +1414,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>February's jobs made $75,710 gross margin (38.6%). Technician time not charged to jobs took ($4,832) and overheads $59,320, leaving $21,222 profit before tax (10.8% of revenue). To cover overheads, jobs need a 27.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -718,571 +1565,421 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>In February maintenance contracts made a 59.6% job gross margin, installations made a 31.2% job gross margin, call-outs and repairs made a 43.8% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 27.7% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Installations: 31.2% gross margin, 3.8 points under the 35.0% target: about $4,851 on $129,300 of revenue in February. Maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B34" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
-        <f>Workings!B115</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (February)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, February 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>Workings!B128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B40" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C40" s="11">
-        <f>Workings!B141</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Job gross margin, February · Maintenance contracts</t>
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C41" s="11">
-        <f>Workings!B154</f>
-        <v/>
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Job gross margin, January · Maintenance contracts</t>
         </is>
       </c>
       <c r="B42" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C42" s="11">
-        <f>Workings!B167</f>
-        <v/>
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B43" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>Workings!B180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B44" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C44" s="11">
-        <f>Workings!B193</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>Workings!B206</f>
-        <v/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, February 2026</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B46" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C46" s="11">
-        <f>Workings!B219</f>
-        <v/>
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B47" s="8">
-        <f>Workings!B233</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>Workings!B232</f>
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B48" s="8">
-        <f>Workings!B246</f>
+        <f>Workings!B142</f>
         <v/>
       </c>
       <c r="C48" s="11">
-        <f>Workings!B245</f>
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B49" s="8">
-        <f>Workings!B259</f>
+        <f>Workings!B155</f>
         <v/>
       </c>
       <c r="C49" s="11">
-        <f>Workings!B258</f>
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B50" s="8">
-        <f>Workings!B272</f>
+        <f>Workings!B168</f>
         <v/>
       </c>
       <c r="C50" s="11">
-        <f>Workings!B271</f>
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B180</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B193</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>Workings!B206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>Workings!B219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B56" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C56" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B58" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C58" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B51" s="8">
+      <c r="B59" s="8">
         <f>Workings!B285</f>
         <v/>
       </c>
-      <c r="C51" s="11">
+      <c r="C59" s="11">
         <f>Workings!B284</f>
         <v/>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>All 13 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="75" ht="45" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in February). All maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Job gross margin, February · Installations</t>
         </is>
       </c>
-      <c r="B61" s="8">
+      <c r="B79" s="8">
         <f>Workings!B294</f>
         <v/>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Job gross margin, January · Installations</t>
-        </is>
-      </c>
-      <c r="B62" s="8">
-        <f>Workings!B303</f>
-        <v/>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B63" s="8">
-        <f>Workings!B319</f>
-        <v/>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (February)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in February 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr"/>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Taringa warehouse EV chargers</t>
-        </is>
-      </c>
-      <c r="B67" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Taringa clinic LED lighting</t>
-        </is>
-      </c>
-      <c r="B68" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>Workings!B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Kedron shop switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B69" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C69" s="11">
-        <f>Workings!B358</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Salisbury gym air-con install</t>
-        </is>
-      </c>
-      <c r="B70" s="8">
-        <f>Workings!B372</f>
-        <v/>
-      </c>
-      <c r="C70" s="11">
-        <f>Workings!B371</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>3 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 22.9% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $18,100 job. Jobs need 27.7% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>3 installations under the 35.0% target, worth about $6,913 between them on $91,500 of revenue. The biggest gap, Kedron shop switchboard upgrade: 24.1% gross margin, 10.9 points under the 35.0% target: about $3,921 on $36,100 of revenue in February. It's below the 27.7% needed to cover overheads, too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Job gross margin, February · Call-outs and repairs</t>
+          <t>Job gross margin, January · Installations</t>
         </is>
       </c>
       <c r="B80" s="8">
-        <f>Workings!B381</f>
+        <f>Workings!B303</f>
         <v/>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -1294,256 +1991,440 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Job gross margin, January · Call-outs and repairs</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B390</f>
+        <f>Workings!B319</f>
         <v/>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B82" s="8">
-        <f>Workings!B406</f>
-        <v/>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
           <t>covers overheads and time not charged (February)</t>
         </is>
       </c>
     </row>
+    <row r="82"/>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Technician time charged, February</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>69.1% of call-out revenue</t>
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in February 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials charged, February</t>
-        </is>
-      </c>
-      <c r="B84" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>$7,020 at cost, plus 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="85"/>
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Taringa warehouse EV chargers</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+    </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, February 2026</t>
-        </is>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Taringa clinic LED lighting</t>
+        </is>
+      </c>
+      <c r="B86" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B345</f>
+        <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="inlineStr"/>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Kedron shop switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B358</f>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Salisbury gym air-con install</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>3 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 22.9% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $18,100 job. Jobs need 27.7% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>3 installations under the 35.0% target, worth about $6,913 between them on $91,500 of revenue. The biggest gap, Kedron shop switchboard upgrade: 24.1% gross margin, 10.9 points under the 35.0% target: about $3,921 on $36,100 of revenue in February. It's below the 27.7% needed to cover overheads, too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Job gross margin, February · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B105" s="8">
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Job gross margin, January · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B106" s="8">
+        <f>Workings!B390</f>
+        <v/>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B107" s="8">
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time charged, February</t>
+        </is>
+      </c>
+      <c r="B108" s="8">
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>69.1% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Materials charged, February</t>
+        </is>
+      </c>
+      <c r="B109" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>$7,020 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, February 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr"/>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>1-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B88" s="8">
+      <c r="B113" s="8">
         <f>Workings!B444</f>
         <v/>
       </c>
-      <c r="C88" s="11">
+      <c r="C113" s="11">
         <f>Workings!B443</f>
         <v/>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B89" s="8">
+      <c r="B114" s="8">
         <f>Workings!B457</f>
         <v/>
       </c>
-      <c r="C89" s="11">
+      <c r="C114" s="11">
         <f>Workings!B456</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>2-hour call-outs (15)</t>
         </is>
       </c>
-      <c r="B90" s="8">
+      <c r="B115" s="8">
         <f>Workings!B470</f>
         <v/>
       </c>
-      <c r="C90" s="11">
+      <c r="C115" s="11">
         <f>Workings!B469</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (4)</t>
         </is>
       </c>
-      <c r="B91" s="8">
+      <c r="B116" s="8">
         <f>Workings!B483</f>
         <v/>
       </c>
-      <c r="C91" s="11">
+      <c r="C116" s="11">
         <f>Workings!B482</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>3-hour call-outs (18)</t>
         </is>
       </c>
-      <c r="B92" s="8">
+      <c r="B117" s="8">
         <f>Workings!B496</f>
         <v/>
       </c>
-      <c r="C92" s="11">
+      <c r="C117" s="11">
         <f>Workings!B495</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>4-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B93" s="8">
+      <c r="B118" s="8">
         <f>Workings!B509</f>
         <v/>
       </c>
-      <c r="C93" s="11">
+      <c r="C118" s="11">
         <f>Workings!B508</f>
         <v/>
       </c>
     </row>
-    <row r="94"/>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>57 call-outs in February billed $20,446 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 43.8% job gross margin between them. Gross margins run from 37.0% to 47.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>All call-outs: 43.8% gross margin, 8.8 points over the 35.0% target ($2,614 ahead on $29,572 in February).</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="12" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104"/>
+    <row r="135"/>
+    <row r="136"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A128:D128"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A98:D98"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="64" min="0" max="16383" man="1"/>
-    <brk id="85" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="70" min="0" max="16383" man="1"/>
+    <brk id="96" min="0" max="16383" man="1"/>
+    <brk id="110" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1572,14 +2453,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1587,7 +2468,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, February 2026</t>
+          <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2615,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, February and January</t>
+          <t>Trades, all lines: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -1819,7 +2700,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, February and January</t>
+          <t>Trades, all lines: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2785,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, February 2026</t>
+          <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
@@ -2249,7 +3130,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, February and January</t>
+          <t>Trades, Maintenance contracts: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -2334,7 +3215,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, February and January</t>
+          <t>Trades, Maintenance contracts: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -2419,7 +3300,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, February 2026</t>
+          <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4838,7 @@
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, February and January</t>
+          <t>Trades, Installations: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -4042,7 +4923,7 @@
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, February and January</t>
+          <t>Trades, Installations: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -4127,7 +5008,7 @@
     <row r="306">
       <c r="A306" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, February 2026</t>
+          <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
@@ -4702,7 +5583,7 @@
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, February and January</t>
+          <t>Trades, Call-outs and repairs: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -4787,7 +5668,7 @@
     <row r="384">
       <c r="A384" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, February and January</t>
+          <t>Trades, Call-outs and repairs: gross margin, February and January</t>
         </is>
       </c>
     </row>
@@ -4872,7 +5753,7 @@
     <row r="393">
       <c r="A393" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, February 2026</t>
+          <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
@@ -5859,7 +6740,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5917,14 +6798,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8961,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8091,5 +8972,9 @@
     <brk id="39" min="0" max="16383" man="1"/>
     <brk id="56" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Job_gross_margin_February_All_jobs">'Report'!$B$15</definedName>
@@ -28,8 +29,8 @@
     <definedName name="Materials_charged_February">'Report'!$B$109</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$134</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$73</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,7 +265,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin by type of job, February 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin by type of job, February 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,6 +332,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 27.7%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$8:$B$9</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$8:$C$9</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -346,6 +495,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.6853999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -353,6 +504,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.6853999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -385,7 +563,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each maintenance contract, February 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each maintenance contract, February 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,6 +616,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$12:$B$13</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$12:$C$13</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 27.7%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$16:$B$17</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$16:$C$17</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -453,6 +779,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -460,6 +788,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -492,7 +847,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in February 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in February 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -587,6 +942,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$20:$B$21</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$20:$C$21</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 27.7%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$24:$B$25</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$24:$C$25</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -602,6 +1105,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.46575"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -609,6 +1114,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.46575"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -641,7 +1173,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on call-outs by length, February 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on call-outs by length, February 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -694,6 +1226,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$28:$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$28:$C$29</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 27.7%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$32:$B$33</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$32:$C$33</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -709,6 +1389,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.5497"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -716,6 +1398,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.5497"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -941,7 +1650,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -963,7 +1672,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="4230000"/>
+    <ext cx="5400000" cy="4446000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -985,7 +1694,7 @@
       <row>83</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1007,7 +1716,7 @@
       <row>111</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1383,7 +2092,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -2411,7 +3120,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2460,7 +3169,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -6740,7 +7449,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6774,6 +7483,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, February 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, February 2026: Break-even 27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, February 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, February 2026: Break-even 27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in February 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in February 2026: Break-even 27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, February 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, February 2026: Break-even 27.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G73"/>
@@ -6805,7 +7727,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -8961,7 +9883,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -295,20 +295,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="0.0%"/>
             <showLegendKey val="0"/>
@@ -409,7 +395,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 27.7%</v>
+            <v>Break-even 33.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -495,7 +481,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6853999999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -509,7 +495,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6853999999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -693,7 +679,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 27.7%</v>
+            <v>Break-even 33.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -779,7 +765,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -793,7 +779,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -877,20 +863,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dPt>
             <idx val="2"/>
             <spPr>
@@ -1019,7 +991,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 27.7%</v>
+            <v>Break-even 33.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1105,7 +1077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.46575"/>
+          <max val="0.5381999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1119,7 +1091,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.46575"/>
+          <max val="0.5381999999999999"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1303,7 +1275,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 27.7%</v>
+            <v>Break-even 33.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1389,7 +1361,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5497"/>
+          <max val="0.60605"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1403,7 +1375,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5497"/>
+          <max val="0.60605"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2092,7 +2064,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2087,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>February's jobs made $75,710 gross margin (38.6%). Technician time not charged to jobs took ($4,832) and overheads $59,320, leaving $21,222 profit before tax (10.8% of revenue). To cover overheads, jobs need a 27.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>February's jobs made $98,246 gross margin (44.9%). Technician time not charged to jobs took $12,920 and overheads $59,320, leaving $26,006 profit before tax (11.9% of revenue). To cover overheads, jobs need a 33.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2102,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2264,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>In February maintenance contracts made a 59.6% job gross margin, installations made a 31.2% job gross margin, call-outs and repairs made a 43.8% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 27.7% just to cover overheads.</t>
+          <t>In February maintenance contracts made a 63.9% job gross margin, installations made a 38.6% job gross margin, call-outs and repairs made a 48.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 33.0% just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2279,7 @@
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Installations: 31.2% gross margin, 3.8 points under the 35.0% target: about $4,851 on $129,300 of revenue in February. Maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
+          <t>Installations: 38.6% gross margin, 3.6 points over the 35.0% target ($5,224 ahead on $144,800 in February). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($12,142 ahead on $42,000 in February).</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2410,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2453,7 +2425,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B50" s="8">
@@ -2468,7 +2440,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2483,7 +2455,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B52" s="8">
@@ -2498,7 +2470,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B53" s="8">
@@ -2528,7 +2500,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -2543,7 +2515,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B56" s="8">
@@ -2621,7 +2593,7 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>All 13 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
+          <t>All 13 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2608,7 @@
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in February). All maintenance contracts: 59.6% gross margin, 24.6 points over the 35.0% target ($9,217 ahead on $37,500 in February).</t>
+          <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in February). All maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($12,142 ahead on $42,000 in February).</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2784,7 @@
     <row r="98" ht="60" customHeight="1">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>3 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 22.9% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $18,100 job. Jobs need 27.7% gross margin just to cover overheads.</t>
+          <t>2 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 31.2% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $20,300 job. Jobs need 33.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2799,7 @@
     <row r="101" ht="60" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>3 installations under the 35.0% target, worth about $6,913 between them on $91,500 of revenue. The biggest gap, Kedron shop switchboard upgrade: 24.1% gross margin, 10.9 points under the 35.0% target: about $3,921 on $36,100 of revenue in February. It's below the 27.7% needed to cover overheads, too.</t>
+          <t>2 installations under the 35.0% target, worth about $1,893 between them on $60,700 of revenue. The biggest gap, Kedron shop switchboard upgrade: 32.2% gross margin, 2.8 points under the 35.0% target: about $1,126 on $40,400 of revenue in February. It's below the 33.0% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2888,7 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>69.1% of call-out revenue</t>
+          <t>71.6% of call-out revenue</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3037,7 @@
     <row r="128" ht="60" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>57 call-outs in February billed $20,446 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 43.8% job gross margin between them. Gross margins run from 37.0% to 47.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>57 call-outs in February billed $22,982 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 48.3% job gross margin between them. Gross margins run from 40.5% to 52.7% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3052,7 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 43.8% gross margin, 8.8 points over the 35.0% target ($2,614 ahead on $29,572 in February).</t>
+          <t>All call-outs: 48.3% gross margin, 13.3 points over the 35.0% target ($4,262 ahead on $32,108 in February).</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3092,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3169,7 +3141,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3175,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>75710</v>
+        <v>98246</v>
       </c>
     </row>
     <row r="9">
@@ -3213,7 +3185,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="10">
@@ -3276,7 +3248,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
     </row>
     <row r="16">
@@ -3315,7 +3287,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3355,10 +3327,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="26">
@@ -3440,10 +3412,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
     </row>
     <row r="35">
@@ -3520,7 +3492,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>75710</v>
+        <v>98246</v>
       </c>
     </row>
     <row r="44">
@@ -3530,7 +3502,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="45">
@@ -3593,7 +3565,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
     </row>
     <row r="51">
@@ -3632,7 +3604,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3639,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="61">
@@ -3733,7 +3705,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
     </row>
     <row r="70">
@@ -3799,7 +3771,7 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
     </row>
     <row r="79">
@@ -3870,10 +3842,10 @@
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="88">
@@ -3955,10 +3927,10 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="97">
@@ -4035,7 +4007,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>75710</v>
+        <v>98246</v>
       </c>
     </row>
     <row r="106">
@@ -4045,7 +4017,7 @@
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="107">
@@ -4108,7 +4080,7 @@
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
     </row>
     <row r="113">
@@ -4147,7 +4119,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4154,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="123">
@@ -4289,7 +4261,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="136">
@@ -4370,7 +4342,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4368,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1800</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="149">
@@ -4406,7 +4378,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-40</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="150">
@@ -4426,7 +4398,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -4477,7 +4449,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4485,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="163">
@@ -4533,7 +4505,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165">
@@ -4584,7 +4556,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4582,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="175">
@@ -4620,7 +4592,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="176">
@@ -4640,7 +4612,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -4691,7 +4663,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4689,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="188">
@@ -4727,7 +4699,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="189">
@@ -4747,7 +4719,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191">
@@ -4798,7 +4770,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4796,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="201">
@@ -4834,7 +4806,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="202">
@@ -4854,7 +4826,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204">
@@ -4931,7 +4903,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="214">
@@ -5012,7 +4984,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5010,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>4200</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="227">
@@ -5048,7 +5020,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-90</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="228">
@@ -5068,7 +5040,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230">
@@ -5119,7 +5091,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5117,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>2800</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="240">
@@ -5155,7 +5127,7 @@
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="241">
@@ -5175,7 +5147,7 @@
         </is>
       </c>
       <c r="B242" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="243">
@@ -5252,7 +5224,7 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="253">
@@ -5359,7 +5331,7 @@
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="266">
@@ -5466,7 +5438,7 @@
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="279">
@@ -5578,10 +5550,10 @@
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="C291" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
     </row>
     <row r="292">
@@ -5663,10 +5635,10 @@
         </is>
       </c>
       <c r="B300" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="C300" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
     </row>
     <row r="301">
@@ -5743,7 +5715,7 @@
         </is>
       </c>
       <c r="B309" s="13" t="n">
-        <v>75710</v>
+        <v>98246</v>
       </c>
     </row>
     <row r="310">
@@ -5753,7 +5725,7 @@
         </is>
       </c>
       <c r="B310" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="311">
@@ -5816,7 +5788,7 @@
         </is>
       </c>
       <c r="B316" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
     </row>
     <row r="317">
@@ -5855,7 +5827,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5862,7 @@
         </is>
       </c>
       <c r="B326" s="13" t="n">
-        <v>37800</v>
+        <v>42300</v>
       </c>
     </row>
     <row r="327">
@@ -5997,7 +5969,7 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>37300</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="340">
@@ -6104,7 +6076,7 @@
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>36100</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="353">
@@ -6211,7 +6183,7 @@
         </is>
       </c>
       <c r="B365" s="13" t="n">
-        <v>18100</v>
+        <v>20300</v>
       </c>
     </row>
     <row r="366">
@@ -6323,10 +6295,10 @@
         </is>
       </c>
       <c r="B378" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="C378" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
     </row>
     <row r="379">
@@ -6408,10 +6380,10 @@
         </is>
       </c>
       <c r="B387" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="C387" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
     </row>
     <row r="388">
@@ -6488,7 +6460,7 @@
         </is>
       </c>
       <c r="B396" s="13" t="n">
-        <v>75710</v>
+        <v>98246</v>
       </c>
     </row>
     <row r="397">
@@ -6498,7 +6470,7 @@
         </is>
       </c>
       <c r="B397" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="398">
@@ -6561,7 +6533,7 @@
         </is>
       </c>
       <c r="B403" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
     </row>
     <row r="404">
@@ -6600,7 +6572,7 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Ties to the February 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the February 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6588,7 @@
     <row r="411">
       <c r="A411" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6631,11 +6603,11 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B413" s="13" t="n">
-        <v>20446</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="414">
@@ -6713,7 +6685,7 @@
     <row r="423">
       <c r="A423" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6700,11 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B425" s="13" t="n">
-        <v>20446</v>
+        <v>22982</v>
       </c>
     </row>
     <row r="426">
@@ -6835,11 +6807,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B438" s="13" t="n">
-        <v>870</v>
+        <v>978</v>
       </c>
     </row>
     <row r="439">
@@ -6942,11 +6914,11 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B451" s="13" t="n">
-        <v>1306</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="452">
@@ -7049,11 +7021,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B464" s="13" t="n">
-        <v>4350</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="465">
@@ -7156,11 +7128,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B477" s="13" t="n">
-        <v>1450</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="478">
@@ -7263,11 +7235,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B490" s="13" t="n">
-        <v>7830</v>
+        <v>8802</v>
       </c>
     </row>
     <row r="491">
@@ -7370,11 +7342,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B503" s="13" t="n">
-        <v>4640</v>
+        <v>5216</v>
       </c>
     </row>
     <row r="504">
@@ -7449,7 +7421,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7523,13 +7495,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report: Job gross margin by type of job, February 2026: Break-even 27.7%</t>
+          <t>Report: Job gross margin by type of job, February 2026: Break-even 33.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7537,7 +7509,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -7571,13 +7543,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each maintenance contract, February 2026: Break-even 27.7%</t>
+          <t>Report: Job gross margin on each maintenance contract, February 2026: Break-even 33.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -7585,7 +7557,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -7619,13 +7591,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each installation invoiced in February 2026: Break-even 27.7%</t>
+          <t>Report: Job gross margin on each installation invoiced in February 2026: Break-even 33.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -7633,7 +7605,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7667,13 +7639,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on call-outs by length, February 2026: Break-even 27.7%</t>
+          <t>Report: Job gross margin on call-outs by length, February 2026: Break-even 33.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -7681,7 +7653,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>0.277</v>
+        <v>0.33</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -7727,7 +7699,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7758,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>114334</v>
@@ -7817,7 +7789,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>113016</v>
@@ -7848,7 +7820,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>85316</v>
@@ -7879,7 +7851,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>80742</v>
@@ -7910,7 +7882,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>102348</v>
@@ -7941,7 +7913,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>85752</v>
@@ -7972,7 +7944,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>76808</v>
@@ -8003,7 +7975,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>83700</v>
@@ -8034,7 +8006,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>97584</v>
@@ -8065,7 +8037,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>120326</v>
@@ -8096,7 +8068,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>78258</v>
@@ -8127,7 +8099,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>80054</v>
@@ -8158,7 +8130,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>79452</v>
@@ -8189,7 +8161,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>115942</v>
@@ -8220,7 +8192,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>84626</v>
@@ -8251,7 +8223,7 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>106590</v>
@@ -8282,7 +8254,7 @@
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>120662</v>
@@ -8313,7 +8285,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>10420</v>
@@ -8344,7 +8316,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>10420</v>
@@ -8375,7 +8347,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>10420</v>
@@ -8406,7 +8378,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>10420</v>
@@ -8437,7 +8409,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>11782</v>
@@ -8468,7 +8440,7 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>11782</v>
@@ -8499,7 +8471,7 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>11782</v>
@@ -8530,7 +8502,7 @@
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>11782</v>
@@ -8561,7 +8533,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>13446</v>
@@ -8592,7 +8564,7 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>13446</v>
@@ -8623,7 +8595,7 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>13446</v>
@@ -8654,7 +8626,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>13446</v>
@@ -8685,7 +8657,7 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>14516</v>
@@ -8716,7 +8688,7 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>14516</v>
@@ -8747,7 +8719,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>14516</v>
@@ -8778,7 +8750,7 @@
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>14516</v>
@@ -8809,7 +8781,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>15158</v>
@@ -8840,7 +8812,7 @@
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>92430</v>
@@ -8871,7 +8843,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>89070</v>
@@ -8902,7 +8874,7 @@
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>59908</v>
@@ -8933,7 +8905,7 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>54678</v>
@@ -8964,7 +8936,7 @@
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>74966</v>
@@ -8995,7 +8967,7 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>61664</v>
@@ -9026,7 +8998,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>52264</v>
@@ -9057,7 +9029,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>59534</v>
@@ -9088,7 +9060,7 @@
         </is>
       </c>
       <c r="D48" s="13" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>72976</v>
@@ -9119,7 +9091,7 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>96920</v>
@@ -9150,7 +9122,7 @@
         </is>
       </c>
       <c r="D50" s="13" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>53590</v>
@@ -9181,7 +9153,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>55440</v>
@@ -9212,7 +9184,7 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E52" s="13" t="n">
         <v>52288</v>
@@ -9243,7 +9215,7 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>87174</v>
@@ -9274,7 +9246,7 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E54" s="13" t="n">
         <v>53408</v>
@@ -9305,7 +9277,7 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>74216</v>
@@ -9336,7 +9308,7 @@
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>88896</v>
@@ -9367,7 +9339,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>11484</v>
@@ -9398,7 +9370,7 @@
         </is>
       </c>
       <c r="D58" s="13" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E58" s="13" t="n">
         <v>13526</v>
@@ -9429,7 +9401,7 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>14988</v>
@@ -9460,7 +9432,7 @@
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E60" s="13" t="n">
         <v>15644</v>
@@ -9491,7 +9463,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>15600</v>
@@ -9522,7 +9494,7 @@
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E62" s="13" t="n">
         <v>12306</v>
@@ -9553,7 +9525,7 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>12762</v>
@@ -9584,7 +9556,7 @@
         </is>
       </c>
       <c r="D64" s="13" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E64" s="13" t="n">
         <v>12384</v>
@@ -9615,7 +9587,7 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>11162</v>
@@ -9646,7 +9618,7 @@
         </is>
       </c>
       <c r="D66" s="13" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E66" s="13" t="n">
         <v>9960</v>
@@ -9677,7 +9649,7 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>11222</v>
@@ -9708,7 +9680,7 @@
         </is>
       </c>
       <c r="D68" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E68" s="13" t="n">
         <v>11168</v>
@@ -9739,7 +9711,7 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>12648</v>
@@ -9770,7 +9742,7 @@
         </is>
       </c>
       <c r="D70" s="13" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E70" s="13" t="n">
         <v>14252</v>
@@ -9801,7 +9773,7 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>16702</v>
@@ -9832,7 +9804,7 @@
         </is>
       </c>
       <c r="D72" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E72" s="13" t="n">
         <v>17858</v>
@@ -9863,7 +9835,7 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>16608</v>
@@ -9883,7 +9855,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-02/job-margins.xlsx
+++ b/media/exports/reports/2026-02/job-margins.xlsx
@@ -13,21 +13,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Job_gross_margin_February_All_jobs">'Report'!$B$15</definedName>
-    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$16</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
-    <definedName name="Job_gross_margin_February_Maintenance_contracts">'Report'!$B$41</definedName>
-    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$42</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
-    <definedName name="Job_gross_margin_February_Installations">'Report'!$B$79</definedName>
-    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$80</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$81</definedName>
-    <definedName name="Job_gross_margin_February_Call_outs_and_repairs">'Report'!$B$105</definedName>
-    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$106</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$107</definedName>
-    <definedName name="Technician_time_charged_February">'Report'!$B$108</definedName>
-    <definedName name="Materials_charged_February">'Report'!$B$109</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$134</definedName>
+    <definedName name="Job_gross_margin_February_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Job_gross_margin_January_All_jobs">'Report'!$B$17</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$18</definedName>
+    <definedName name="Job_gross_margin_February_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Job_gross_margin_January_Maintenance_contracts">'Report'!$B$43</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$44</definedName>
+    <definedName name="Job_gross_margin_February_Installations">'Report'!$B$80</definedName>
+    <definedName name="Job_gross_margin_January_Installations">'Report'!$B$81</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$82</definedName>
+    <definedName name="Job_gross_margin_February_Call_outs_and_repairs">'Report'!$B$106</definedName>
+    <definedName name="Job_gross_margin_January_Call_outs_and_repairs">'Report'!$B$107</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$108</definedName>
+    <definedName name="Technician_time_charged_February">'Report'!$B$109</definedName>
+    <definedName name="Materials_charged_February">'Report'!$B$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$135</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$509</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$73</definedName>
@@ -67,6 +67,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
@@ -92,11 +97,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,36 +129,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,12 +308,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$21:$A$23</f>
+              <f>'Report'!$A$22:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$21:$B$23</f>
+              <f>'Report'!$B$22:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -589,12 +592,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$47:$A$59</f>
+              <f>'Report'!$A$48:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$47:$B$59</f>
+              <f>'Report'!$B$48:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -901,12 +904,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$85:$A$88</f>
+              <f>'Report'!$A$86:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$85:$B$88</f>
+              <f>'Report'!$B$86:$B$89</f>
             </numRef>
           </val>
         </ser>
@@ -1185,12 +1188,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$113:$A$118</f>
+              <f>'Report'!$A$114:$A$119</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$113:$B$118</f>
+              <f>'Report'!$B$114:$B$119</f>
             </numRef>
           </val>
         </ser>
@@ -1619,7 +1622,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1641,7 +1644,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="4446000"/>
@@ -1663,7 +1666,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1685,7 +1688,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2556000"/>
@@ -2038,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2064,7 +2067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2072,92 +2075,83 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Jobs made a 44.9% gross margin in February: maintenance contracts the most (63.9%), installations the least (38.6%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>From gross margin to profit</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>February's jobs made $98,246 gross margin (44.9%). Technician time not charged to jobs took $12,920 and overheads $59,320, leaving $26,006 profit before tax (11.9% of revenue). To cover overheads, jobs need a 33.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Gross margin, not profit</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: All jobs</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Type of job: All jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · All jobs</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Job gross margin, January · All jobs</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+          <t>Job gross margin, February · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2166,86 +2160,101 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Job gross margin, January · All jobs</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!C37</f>
+        <v/>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B18" s="9">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (February)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, February 2026</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>Workings!B63</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B62</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>Workings!B72</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>Workings!B71</f>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B24" s="9">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="12">
         <f>Workings!B80</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -2254,87 +2263,72 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>In February maintenance contracts made a 63.9% job gross margin, installations made a 38.6% job gross margin, call-outs and repairs made a 48.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 33.0% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Installations: 38.6% gross margin, 3.6 points over the 35.0% target ($5,224 ahead on $144,800 in February). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($12,142 ahead on $42,000 in February).</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Maintenance contracts</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Maintenance contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B41" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Job gross margin, January · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B42" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>Job gross margin, February · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2343,236 +2337,251 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Job gross margin, January · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>Workings!C99</f>
+        <v/>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B43" s="8">
+      <c r="B44" s="9">
         <f>Workings!B115</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (February)</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each maintenance contract, February 2026</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
-        </is>
-      </c>
-      <c r="B47" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C47" s="11">
-        <f>Workings!B128</f>
-        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B48" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C48" s="11">
-        <f>Workings!B141</f>
+          <t>Carindale vet clinic</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>Workings!B129</f>
+        <v/>
+      </c>
+      <c r="C48" s="12">
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>Workings!B154</f>
+          <t>Wynnum medical centre</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>Workings!B142</f>
+        <v/>
+      </c>
+      <c r="C49" s="12">
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B50" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C50" s="11">
-        <f>Workings!B167</f>
+          <t>Ashgrove aged care</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>Workings!B155</f>
+        <v/>
+      </c>
+      <c r="C50" s="12">
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C51" s="11">
-        <f>Workings!B180</f>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B51" s="9">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C51" s="12">
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C52" s="11">
-        <f>Workings!B193</f>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B52" s="9">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C52" s="12">
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C53" s="11">
-        <f>Workings!B206</f>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C53" s="12">
+        <f>Workings!B193</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B54" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C54" s="11">
-        <f>Workings!B219</f>
+          <t>Southbank cafe group</t>
+        </is>
+      </c>
+      <c r="B54" s="9">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C54" s="12">
+        <f>Workings!B206</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
-        </is>
-      </c>
-      <c r="B55" s="8">
-        <f>Workings!B233</f>
-        <v/>
-      </c>
-      <c r="C55" s="11">
-        <f>Workings!B232</f>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B55" s="9">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C55" s="12">
+        <f>Workings!B219</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B246</f>
-        <v/>
-      </c>
-      <c r="C56" s="11">
-        <f>Workings!B245</f>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B56" s="9">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>Workings!B232</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>West End brewery</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>Workings!B259</f>
-        <v/>
-      </c>
-      <c r="C57" s="11">
-        <f>Workings!B258</f>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C57" s="12">
+        <f>Workings!B245</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
-        </is>
-      </c>
-      <c r="B58" s="8">
-        <f>Workings!B272</f>
-        <v/>
-      </c>
-      <c r="C58" s="11">
-        <f>Workings!B271</f>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>Workings!B258</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C59" s="12">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B59" s="8">
+      <c r="B60" s="9">
         <f>Workings!B285</f>
         <v/>
       </c>
-      <c r="C59" s="11">
+      <c r="C60" s="12">
         <f>Workings!B284</f>
         <v/>
       </c>
     </row>
-    <row r="60"/>
     <row r="61"/>
     <row r="62"/>
     <row r="63"/>
@@ -2583,87 +2592,72 @@
     <row r="68"/>
     <row r="69"/>
     <row r="70"/>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>All 13 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in February). All maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($12,142 ahead on $42,000 in February).</t>
         </is>
       </c>
     </row>
-    <row r="76"/>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
+    <row r="77"/>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Installations</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>Workings!B294</f>
-        <v/>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Job gross margin, January · Installations</t>
-        </is>
-      </c>
-      <c r="B80" s="8">
-        <f>Workings!B303</f>
-        <v/>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
+          <t>Job gross margin, February · Installations</t>
+        </is>
+      </c>
+      <c r="B80" s="9">
+        <f>Workings!B294</f>
+        <v/>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2672,101 +2666,116 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Job gross margin, January · Installations</t>
+        </is>
+      </c>
+      <c r="B81" s="9">
+        <f>Workings!C303</f>
+        <v/>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B81" s="8">
+      <c r="B82" s="9">
         <f>Workings!B319</f>
         <v/>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (February)</t>
         </is>
       </c>
     </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each installation invoiced in February 2026</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr"/>
-      <c r="B84" s="7" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr"/>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Taringa warehouse EV chargers</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B332</f>
-        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Taringa clinic LED lighting</t>
-        </is>
-      </c>
-      <c r="B86" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B345</f>
+          <t>Taringa warehouse EV chargers</t>
+        </is>
+      </c>
+      <c r="B86" s="9">
+        <f>Workings!B333</f>
+        <v/>
+      </c>
+      <c r="C86" s="12">
+        <f>Workings!B332</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kedron shop switchboard upgrade</t>
-        </is>
-      </c>
-      <c r="B87" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C87" s="11">
-        <f>Workings!B358</f>
+          <t>Taringa clinic LED lighting</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C87" s="12">
+        <f>Workings!B345</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Kedron shop switchboard upgrade</t>
+        </is>
+      </c>
+      <c r="B88" s="9">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C88" s="12">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>Salisbury gym air-con install</t>
         </is>
       </c>
-      <c r="B88" s="8">
+      <c r="B89" s="9">
         <f>Workings!B372</f>
         <v/>
       </c>
-      <c r="C88" s="11">
+      <c r="C89" s="12">
         <f>Workings!B371</f>
         <v/>
       </c>
     </row>
-    <row r="89"/>
     <row r="90"/>
     <row r="91"/>
     <row r="92"/>
@@ -2774,87 +2783,72 @@
     <row r="94"/>
     <row r="95"/>
     <row r="96"/>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>2 of the 4 installation jobs invoiced in February made less than the 35.0% job gross margin target. The Salisbury gym air-con install made a 31.2% job gross margin: 71.5 h of technician time ($4,862) and $1,300 of subcontractors on a $20,300 job. Jobs need 33.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>2 installations under the 35.0% target, worth about $1,893 between them on $60,700 of revenue. The biggest gap, Kedron shop switchboard upgrade: 32.2% gross margin, 2.8 points under the 35.0% target: about $1,126 on $40,400 of revenue in February. It's below the 33.0% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Job gross margin, February · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B105" s="8">
-        <f>Workings!B381</f>
-        <v/>
-      </c>
-      <c r="C105" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Job gross margin, January · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B106" s="8">
-        <f>Workings!B390</f>
-        <v/>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
+          <t>Job gross margin, February · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B106" s="9">
+        <f>Workings!B381</f>
+        <v/>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2863,163 +2857,178 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B107" s="8">
-        <f>Workings!B406</f>
-        <v/>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (February)</t>
+          <t>Job gross margin, January · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B107" s="9">
+        <f>Workings!C390</f>
+        <v/>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technician time charged, February</t>
-        </is>
-      </c>
-      <c r="B108" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>71.6% of call-out revenue</t>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B108" s="9">
+        <f>Workings!B406</f>
+        <v/>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (February)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>Technician time charged, February</t>
+        </is>
+      </c>
+      <c r="B109" s="12">
+        <f>Workings!B413</f>
+        <v/>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>71.6% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>Materials charged, February</t>
         </is>
       </c>
-      <c r="B109" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="B110" s="12">
+        <f>Workings!B429</f>
+        <v/>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>$7,020 at cost, plus 30%</t>
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, February 2026</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr"/>
-      <c r="B112" s="7" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr"/>
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (6)</t>
-        </is>
-      </c>
-      <c r="B113" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C113" s="11">
-        <f>Workings!B443</f>
-        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (6)</t>
-        </is>
-      </c>
-      <c r="B114" s="8">
-        <f>Workings!B457</f>
-        <v/>
-      </c>
-      <c r="C114" s="11">
-        <f>Workings!B456</f>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+      <c r="B114" s="9">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C114" s="12">
+        <f>Workings!B443</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2-hour call-outs (15)</t>
-        </is>
-      </c>
-      <c r="B115" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C115" s="11">
-        <f>Workings!B469</f>
+          <t>1.5-hour call-outs (6)</t>
+        </is>
+      </c>
+      <c r="B115" s="9">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>Workings!B456</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (4)</t>
-        </is>
-      </c>
-      <c r="B116" s="8">
-        <f>Workings!B483</f>
-        <v/>
-      </c>
-      <c r="C116" s="11">
-        <f>Workings!B482</f>
+          <t>2-hour call-outs (15)</t>
+        </is>
+      </c>
+      <c r="B116" s="9">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>Workings!B469</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3-hour call-outs (18)</t>
-        </is>
-      </c>
-      <c r="B117" s="8">
-        <f>Workings!B496</f>
-        <v/>
-      </c>
-      <c r="C117" s="11">
-        <f>Workings!B495</f>
+          <t>2.5-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B117" s="9">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C117" s="12">
+        <f>Workings!B482</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>3-hour call-outs (18)</t>
+        </is>
+      </c>
+      <c r="B118" s="9">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C118" s="12">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>4-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B118" s="8">
+      <c r="B119" s="9">
         <f>Workings!B509</f>
         <v/>
       </c>
-      <c r="C118" s="11">
+      <c r="C119" s="12">
         <f>Workings!B508</f>
         <v/>
       </c>
     </row>
-    <row r="119"/>
     <row r="120"/>
     <row r="121"/>
     <row r="122"/>
@@ -3027,83 +3036,85 @@
     <row r="124"/>
     <row r="125"/>
     <row r="126"/>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>57 call-outs in February billed $22,982 of technician time and $9,126 of materials ($7,020 at cost plus 30%), and made a 48.3% job gross margin between them. Gross margins run from 40.5% to 52.7% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="129"/>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="30" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>All call-outs: 48.3% gross margin, 13.3 points over the 35.0% target ($4,262 ahead on $32,108 in February).</t>
         </is>
       </c>
     </row>
-    <row r="132"/>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="12" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="13" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="135"/>
     <row r="136"/>
+    <row r="137"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A131:D131"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="5" manualBreakCount="5">
-    <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="70" min="0" max="16383" man="1"/>
-    <brk id="96" min="0" max="16383" man="1"/>
-    <brk id="110" min="0" max="16383" man="1"/>
+    <brk id="19" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="71" min="0" max="16383" man="1"/>
+    <brk id="97" min="0" max="16383" man="1"/>
+    <brk id="111" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3141,28 +3152,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -3174,7 +3185,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>98246</v>
       </c>
     </row>
@@ -3184,7 +3195,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3194,7 +3205,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>59432</v>
       </c>
     </row>
@@ -3204,7 +3215,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -3215,7 +3226,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>B8-B11</f>
         <v/>
       </c>
@@ -3226,7 +3237,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>59320</v>
       </c>
     </row>
@@ -3236,7 +3247,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>B12-B13</f>
         <v/>
       </c>
@@ -3247,7 +3258,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>218908</v>
       </c>
     </row>
@@ -3257,7 +3268,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B8/B15</f>
         <v/>
       </c>
@@ -3268,18 +3279,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <f>(B11+B13)/B15</f>
         <v/>
       </c>
@@ -3294,27 +3305,27 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -3326,10 +3337,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>218908</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -3339,10 +3350,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>120662</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>106590</v>
       </c>
     </row>
@@ -3352,26 +3363,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <f>B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <f>C25-C26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/B25</f>
         <v/>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <f>C27/C25</f>
         <v/>
       </c>
@@ -3379,27 +3390,27 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -3411,10 +3422,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="n">
         <v>218908</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <v>183306</v>
       </c>
     </row>
@@ -3424,10 +3435,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>120662</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>106590</v>
       </c>
     </row>
@@ -3437,26 +3448,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>C34-C35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <f>B36/B34</f>
         <v/>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <f>C36/C34</f>
         <v/>
       </c>
@@ -3464,22 +3475,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -3491,7 +3502,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>98246</v>
       </c>
     </row>
@@ -3501,7 +3512,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3511,7 +3522,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>59432</v>
       </c>
     </row>
@@ -3521,7 +3532,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>B44-B45</f>
         <v/>
       </c>
@@ -3532,7 +3543,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <f>B43-B46</f>
         <v/>
       </c>
@@ -3543,7 +3554,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>59320</v>
       </c>
     </row>
@@ -3553,7 +3564,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47-B48</f>
         <v/>
       </c>
@@ -3564,7 +3575,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="B50" s="14" t="n">
         <v>218908</v>
       </c>
     </row>
@@ -3574,7 +3585,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <f>B43/B50</f>
         <v/>
       </c>
@@ -3585,18 +3596,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <f>B49/B50</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <f>(B46+B48)/B50</f>
         <v/>
       </c>
@@ -3611,22 +3622,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Maintenance contracts, February</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -3638,7 +3649,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>42000</v>
       </c>
     </row>
@@ -3648,7 +3659,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="14" t="n">
         <v>15158</v>
       </c>
     </row>
@@ -3658,18 +3669,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60-B61</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <f>B62/B60</f>
         <v/>
       </c>
@@ -3677,22 +3688,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Installations, February</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -3704,7 +3715,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B69" s="13" t="n">
+      <c r="B69" s="14" t="n">
         <v>144800</v>
       </c>
     </row>
@@ -3714,7 +3725,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B70" s="13" t="n">
+      <c r="B70" s="14" t="n">
         <v>88896</v>
       </c>
     </row>
@@ -3724,18 +3735,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <f>B69-B70</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <f>B71/B69</f>
         <v/>
       </c>
@@ -3743,22 +3754,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Call-outs and repairs, February</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -3770,7 +3781,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B78" s="13" t="n">
+      <c r="B78" s="14" t="n">
         <v>32108</v>
       </c>
     </row>
@@ -3780,7 +3791,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n">
+      <c r="B79" s="14" t="n">
         <v>16608</v>
       </c>
     </row>
@@ -3790,18 +3801,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="14">
         <f>B78-B79</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <f>B80/B78</f>
         <v/>
       </c>
@@ -3809,27 +3820,27 @@
     <row r="82"/>
     <row r="83"/>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -3841,10 +3852,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B87" s="13" t="n">
+      <c r="B87" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3854,10 +3865,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B88" s="13" t="n">
+      <c r="B88" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3867,26 +3878,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="14">
         <f>B87-B88</f>
         <v/>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="14">
         <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <f>B89/B87</f>
         <v/>
       </c>
-      <c r="C90" s="16">
+      <c r="C90" s="17">
         <f>C89/C87</f>
         <v/>
       </c>
@@ -3894,27 +3905,27 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -3926,10 +3937,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B96" s="13" t="n">
+      <c r="B96" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="C96" s="13" t="n">
+      <c r="C96" s="14" t="n">
         <v>40100</v>
       </c>
     </row>
@@ -3939,10 +3950,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B97" s="13" t="n">
+      <c r="B97" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="14" t="n">
         <v>14516</v>
       </c>
     </row>
@@ -3952,26 +3963,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="14">
         <f>B96-B97</f>
         <v/>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="14">
         <f>C96-C97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <f>B98/B96</f>
         <v/>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="17">
         <f>C98/C96</f>
         <v/>
       </c>
@@ -3979,22 +3990,22 @@
     <row r="100"/>
     <row r="101"/>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr"/>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -4006,7 +4017,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B105" s="13" t="n">
+      <c r="B105" s="14" t="n">
         <v>98246</v>
       </c>
     </row>
@@ -4016,7 +4027,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B106" s="13" t="n">
+      <c r="B106" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -4026,7 +4037,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B107" s="13" t="n">
+      <c r="B107" s="14" t="n">
         <v>59432</v>
       </c>
     </row>
@@ -4036,7 +4047,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="14">
         <f>B106-B107</f>
         <v/>
       </c>
@@ -4047,7 +4058,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="14">
         <f>B105-B108</f>
         <v/>
       </c>
@@ -4058,7 +4069,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B110" s="13" t="n">
+      <c r="B110" s="14" t="n">
         <v>59320</v>
       </c>
     </row>
@@ -4068,7 +4079,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="14">
         <f>B109-B110</f>
         <v/>
       </c>
@@ -4079,7 +4090,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B112" s="13" t="n">
+      <c r="B112" s="14" t="n">
         <v>218908</v>
       </c>
     </row>
@@ -4089,7 +4100,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B113" s="14">
+      <c r="B113" s="15">
         <f>B105/B112</f>
         <v/>
       </c>
@@ -4100,18 +4111,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B114" s="14">
+      <c r="B114" s="15">
         <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <f>(B108+B110)/B112</f>
         <v/>
       </c>
@@ -4126,22 +4137,22 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Carindale vet clinic</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="12" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr"/>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4153,7 +4164,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B122" s="13" t="n">
+      <c r="B122" s="14" t="n">
         <v>1900</v>
       </c>
     </row>
@@ -4163,7 +4174,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B123" s="13" t="n">
+      <c r="B123" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4173,7 +4184,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B124" s="13" t="n">
+      <c r="B124" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4183,7 +4194,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B125" s="17" t="n">
+      <c r="B125" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4193,7 +4204,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B126" s="13" t="n">
+      <c r="B126" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4203,7 +4214,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="14">
         <f>-B125*B126</f>
         <v/>
       </c>
@@ -4214,18 +4225,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="14">
         <f>B122+B123+B124+B127</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <f>B128/B122</f>
         <v/>
       </c>
@@ -4233,22 +4244,22 @@
     <row r="130"/>
     <row r="131"/>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="12" t="inlineStr">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr"/>
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4260,7 +4271,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B135" s="13" t="n">
+      <c r="B135" s="14" t="n">
         <v>2450</v>
       </c>
     </row>
@@ -4270,7 +4281,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B136" s="13" t="n">
+      <c r="B136" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4280,7 +4291,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B137" s="13" t="n">
+      <c r="B137" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4290,7 +4301,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B138" s="17" t="n">
+      <c r="B138" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4300,7 +4311,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B139" s="13" t="n">
+      <c r="B139" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4310,7 +4321,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="14">
         <f>-B138*B139</f>
         <v/>
       </c>
@@ -4321,18 +4332,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="14">
         <f>B135+B136+B137+B140</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <f>B141/B135</f>
         <v/>
       </c>
@@ -4340,22 +4351,22 @@
     <row r="143"/>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr"/>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4367,7 +4378,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B148" s="13" t="n">
+      <c r="B148" s="14" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -4377,7 +4388,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B149" s="13" t="n">
+      <c r="B149" s="14" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -4387,7 +4398,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n">
+      <c r="B150" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4397,7 +4408,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B151" s="17" t="n">
+      <c r="B151" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4407,7 +4418,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B152" s="13" t="n">
+      <c r="B152" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4417,7 +4428,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="14">
         <f>-B151*B152</f>
         <v/>
       </c>
@@ -4428,18 +4439,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="14">
         <f>B148+B149+B150+B153</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="15" t="inlineStr">
+      <c r="A155" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <f>B154/B148</f>
         <v/>
       </c>
@@ -4447,22 +4458,22 @@
     <row r="156"/>
     <row r="157"/>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr"/>
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4474,7 +4485,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B161" s="13" t="n">
+      <c r="B161" s="14" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -4484,7 +4495,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B162" s="13" t="n">
+      <c r="B162" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4494,7 +4505,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B163" s="13" t="n">
+      <c r="B163" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4504,7 +4515,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B164" s="17" t="n">
+      <c r="B164" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4514,7 +4525,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B165" s="13" t="n">
+      <c r="B165" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4524,7 +4535,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="14">
         <f>-B164*B165</f>
         <v/>
       </c>
@@ -4535,18 +4546,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="14">
         <f>B161+B162+B163+B166</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <f>B167/B161</f>
         <v/>
       </c>
@@ -4554,22 +4565,22 @@
     <row r="169"/>
     <row r="170"/>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="inlineStr">
+      <c r="A172" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr"/>
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4581,7 +4592,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B174" s="13" t="n">
+      <c r="B174" s="14" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -4591,7 +4602,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B175" s="13" t="n">
+      <c r="B175" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4601,7 +4612,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B176" s="13" t="n">
+      <c r="B176" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4611,7 +4622,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B177" s="17" t="n">
+      <c r="B177" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4621,7 +4632,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B178" s="13" t="n">
+      <c r="B178" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4631,7 +4642,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="14">
         <f>-B177*B178</f>
         <v/>
       </c>
@@ -4642,18 +4653,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="14">
         <f>B174+B175+B176+B179</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="15" t="inlineStr">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <f>B180/B174</f>
         <v/>
       </c>
@@ -4661,22 +4672,22 @@
     <row r="182"/>
     <row r="183"/>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr"/>
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4688,7 +4699,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B187" s="13" t="n">
+      <c r="B187" s="14" t="n">
         <v>3800</v>
       </c>
     </row>
@@ -4698,7 +4709,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B188" s="13" t="n">
+      <c r="B188" s="14" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -4708,7 +4719,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B189" s="13" t="n">
+      <c r="B189" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4718,7 +4729,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B190" s="17" t="n">
+      <c r="B190" s="18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4728,7 +4739,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B191" s="13" t="n">
+      <c r="B191" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4738,7 +4749,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="14">
         <f>-B190*B191</f>
         <v/>
       </c>
@@ -4749,18 +4760,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="14">
         <f>B187+B188+B189+B192</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
+      <c r="A194" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <f>B193/B187</f>
         <v/>
       </c>
@@ -4768,22 +4779,22 @@
     <row r="195"/>
     <row r="196"/>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="inlineStr">
+      <c r="A198" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr"/>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="A199" s="7" t="inlineStr"/>
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4795,7 +4806,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B200" s="13" t="n">
+      <c r="B200" s="14" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -4805,7 +4816,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B201" s="13" t="n">
+      <c r="B201" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4815,7 +4826,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B202" s="13" t="n">
+      <c r="B202" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4825,7 +4836,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B203" s="17" t="n">
+      <c r="B203" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4835,7 +4846,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B204" s="13" t="n">
+      <c r="B204" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4845,7 +4856,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="14">
         <f>-B203*B204</f>
         <v/>
       </c>
@@ -4856,18 +4867,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="14">
         <f>B200+B201+B202+B205</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="15" t="inlineStr">
+      <c r="A207" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <f>B206/B200</f>
         <v/>
       </c>
@@ -4875,22 +4886,22 @@
     <row r="208"/>
     <row r="209"/>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="12" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr"/>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="A212" s="7" t="inlineStr"/>
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4902,7 +4913,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B213" s="13" t="n">
+      <c r="B213" s="14" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -4912,7 +4923,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B214" s="13" t="n">
+      <c r="B214" s="14" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4922,7 +4933,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B215" s="13" t="n">
+      <c r="B215" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4932,7 +4943,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B216" s="17" t="n">
+      <c r="B216" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4942,7 +4953,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B217" s="13" t="n">
+      <c r="B217" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4952,7 +4963,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="14">
         <f>-B216*B217</f>
         <v/>
       </c>
@@ -4963,18 +4974,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="14">
         <f>B213+B214+B215+B218</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <f>B219/B213</f>
         <v/>
       </c>
@@ -4982,22 +4993,22 @@
     <row r="221"/>
     <row r="222"/>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="12" t="inlineStr">
+      <c r="A224" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="A225" s="7" t="inlineStr"/>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5009,7 +5020,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B226" s="13" t="n">
+      <c r="B226" s="14" t="n">
         <v>3150</v>
       </c>
     </row>
@@ -5019,7 +5030,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B227" s="13" t="n">
+      <c r="B227" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -5029,7 +5040,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B228" s="13" t="n">
+      <c r="B228" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5039,7 +5050,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B229" s="17" t="n">
+      <c r="B229" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5049,7 +5060,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B230" s="13" t="n">
+      <c r="B230" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5059,7 +5070,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="14">
         <f>-B229*B230</f>
         <v/>
       </c>
@@ -5070,18 +5081,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="14">
         <f>B226+B227+B228+B231</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="15" t="inlineStr">
+      <c r="A233" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <f>B232/B226</f>
         <v/>
       </c>
@@ -5089,22 +5100,22 @@
     <row r="234"/>
     <row r="235"/>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="12" t="inlineStr">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr"/>
-      <c r="B238" s="7" t="inlineStr">
+      <c r="A238" s="7" t="inlineStr"/>
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5116,7 +5127,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B239" s="13" t="n">
+      <c r="B239" s="14" t="n">
         <v>4700</v>
       </c>
     </row>
@@ -5126,7 +5137,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B240" s="13" t="n">
+      <c r="B240" s="14" t="n">
         <v>-90</v>
       </c>
     </row>
@@ -5136,7 +5147,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B241" s="13" t="n">
+      <c r="B241" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5146,7 +5157,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B242" s="17" t="n">
+      <c r="B242" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5156,7 +5167,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B243" s="13" t="n">
+      <c r="B243" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5166,7 +5177,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B244" s="13">
+      <c r="B244" s="14">
         <f>-B242*B243</f>
         <v/>
       </c>
@@ -5177,18 +5188,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B245" s="13">
+      <c r="B245" s="14">
         <f>B239+B240+B241+B244</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr">
+      <c r="A246" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <f>B245/B239</f>
         <v/>
       </c>
@@ -5196,22 +5207,22 @@
     <row r="247"/>
     <row r="248"/>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="12" t="inlineStr">
+      <c r="A250" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr"/>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr"/>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5223,7 +5234,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B252" s="13" t="n">
+      <c r="B252" s="14" t="n">
         <v>2900</v>
       </c>
     </row>
@@ -5233,7 +5244,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B253" s="13" t="n">
+      <c r="B253" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5243,7 +5254,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B254" s="13" t="n">
+      <c r="B254" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5253,7 +5264,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B255" s="17" t="n">
+      <c r="B255" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5263,7 +5274,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B256" s="13" t="n">
+      <c r="B256" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5273,7 +5284,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B257" s="13">
+      <c r="B257" s="14">
         <f>-B255*B256</f>
         <v/>
       </c>
@@ -5284,18 +5295,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B258" s="13">
+      <c r="B258" s="14">
         <f>B252+B253+B254+B257</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="15" t="inlineStr">
+      <c r="A259" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <f>B258/B252</f>
         <v/>
       </c>
@@ -5303,22 +5314,22 @@
     <row r="260"/>
     <row r="261"/>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="A263" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr"/>
-      <c r="B264" s="7" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr"/>
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5330,7 +5341,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B265" s="13" t="n">
+      <c r="B265" s="14" t="n">
         <v>4350</v>
       </c>
     </row>
@@ -5340,7 +5351,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B266" s="13" t="n">
+      <c r="B266" s="14" t="n">
         <v>-110</v>
       </c>
     </row>
@@ -5350,7 +5361,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B267" s="13" t="n">
+      <c r="B267" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5360,7 +5371,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B268" s="17" t="n">
+      <c r="B268" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5370,7 +5381,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B269" s="13" t="n">
+      <c r="B269" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5380,7 +5391,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B270" s="13">
+      <c r="B270" s="14">
         <f>-B268*B269</f>
         <v/>
       </c>
@@ -5391,18 +5402,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B271" s="13">
+      <c r="B271" s="14">
         <f>B265+B266+B267+B270</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr">
+      <c r="A272" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <f>B271/B265</f>
         <v/>
       </c>
@@ -5410,22 +5421,22 @@
     <row r="273"/>
     <row r="274"/>
     <row r="275">
-      <c r="A275" s="5" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="12" t="inlineStr">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr"/>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="A277" s="7" t="inlineStr"/>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5437,7 +5448,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B278" s="13" t="n">
+      <c r="B278" s="14" t="n">
         <v>2700</v>
       </c>
     </row>
@@ -5447,7 +5458,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B279" s="13" t="n">
+      <c r="B279" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5457,7 +5468,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B280" s="13" t="n">
+      <c r="B280" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5467,7 +5478,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B281" s="17" t="n">
+      <c r="B281" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5477,7 +5488,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B282" s="13" t="n">
+      <c r="B282" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5487,7 +5498,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B283" s="13">
+      <c r="B283" s="14">
         <f>-B281*B282</f>
         <v/>
       </c>
@@ -5498,18 +5509,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B284" s="13">
+      <c r="B284" s="14">
         <f>B278+B279+B280+B283</f>
         <v/>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="15" t="inlineStr">
+      <c r="A285" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="17">
         <f>B284/B278</f>
         <v/>
       </c>
@@ -5517,27 +5528,27 @@
     <row r="286"/>
     <row r="287"/>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
+      <c r="A288" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="12" t="inlineStr">
+      <c r="A289" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr"/>
-      <c r="B290" s="7" t="inlineStr">
+      <c r="A290" s="7" t="inlineStr"/>
+      <c r="B290" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C290" s="7" t="inlineStr">
+      <c r="C290" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -5549,10 +5560,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B291" s="13" t="n">
+      <c r="B291" s="14" t="n">
         <v>144800</v>
       </c>
-      <c r="C291" s="13" t="n">
+      <c r="C291" s="14" t="n">
         <v>109100</v>
       </c>
     </row>
@@ -5562,10 +5573,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B292" s="13" t="n">
+      <c r="B292" s="14" t="n">
         <v>88896</v>
       </c>
-      <c r="C292" s="13" t="n">
+      <c r="C292" s="14" t="n">
         <v>74216</v>
       </c>
     </row>
@@ -5575,26 +5586,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B293" s="13">
+      <c r="B293" s="14">
         <f>B291-B292</f>
         <v/>
       </c>
-      <c r="C293" s="13">
+      <c r="C293" s="14">
         <f>C291-C292</f>
         <v/>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="15" t="inlineStr">
+      <c r="A294" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B294" s="16">
+      <c r="B294" s="17">
         <f>B293/B291</f>
         <v/>
       </c>
-      <c r="C294" s="16">
+      <c r="C294" s="17">
         <f>C293/C291</f>
         <v/>
       </c>
@@ -5602,27 +5613,27 @@
     <row r="295"/>
     <row r="296"/>
     <row r="297">
-      <c r="A297" s="5" t="inlineStr">
+      <c r="A297" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="12" t="inlineStr">
+      <c r="A298" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr"/>
-      <c r="B299" s="7" t="inlineStr">
+      <c r="A299" s="7" t="inlineStr"/>
+      <c r="B299" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C299" s="7" t="inlineStr">
+      <c r="C299" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -5634,10 +5645,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B300" s="13" t="n">
+      <c r="B300" s="14" t="n">
         <v>144800</v>
       </c>
-      <c r="C300" s="13" t="n">
+      <c r="C300" s="14" t="n">
         <v>109100</v>
       </c>
     </row>
@@ -5647,10 +5658,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B301" s="13" t="n">
+      <c r="B301" s="14" t="n">
         <v>88896</v>
       </c>
-      <c r="C301" s="13" t="n">
+      <c r="C301" s="14" t="n">
         <v>74216</v>
       </c>
     </row>
@@ -5660,26 +5671,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B302" s="13">
+      <c r="B302" s="14">
         <f>B300-B301</f>
         <v/>
       </c>
-      <c r="C302" s="13">
+      <c r="C302" s="14">
         <f>C300-C301</f>
         <v/>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="15" t="inlineStr">
+      <c r="A303" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B303" s="16">
+      <c r="B303" s="17">
         <f>B302/B300</f>
         <v/>
       </c>
-      <c r="C303" s="16">
+      <c r="C303" s="17">
         <f>C302/C300</f>
         <v/>
       </c>
@@ -5687,22 +5698,22 @@
     <row r="304"/>
     <row r="305"/>
     <row r="306">
-      <c r="A306" s="5" t="inlineStr">
+      <c r="A306" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="12" t="inlineStr">
+      <c r="A307" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="6" t="inlineStr"/>
-      <c r="B308" s="7" t="inlineStr">
+      <c r="A308" s="7" t="inlineStr"/>
+      <c r="B308" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -5714,7 +5725,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B309" s="13" t="n">
+      <c r="B309" s="14" t="n">
         <v>98246</v>
       </c>
     </row>
@@ -5724,7 +5735,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B310" s="13" t="n">
+      <c r="B310" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -5734,7 +5745,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B311" s="13" t="n">
+      <c r="B311" s="14" t="n">
         <v>59432</v>
       </c>
     </row>
@@ -5744,7 +5755,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B312" s="13">
+      <c r="B312" s="14">
         <f>B310-B311</f>
         <v/>
       </c>
@@ -5755,7 +5766,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B313" s="13">
+      <c r="B313" s="14">
         <f>B309-B312</f>
         <v/>
       </c>
@@ -5766,7 +5777,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B314" s="13" t="n">
+      <c r="B314" s="14" t="n">
         <v>59320</v>
       </c>
     </row>
@@ -5776,7 +5787,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B315" s="13">
+      <c r="B315" s="14">
         <f>B313-B314</f>
         <v/>
       </c>
@@ -5787,7 +5798,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B316" s="13" t="n">
+      <c r="B316" s="14" t="n">
         <v>218908</v>
       </c>
     </row>
@@ -5797,7 +5808,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B317" s="14">
+      <c r="B317" s="15">
         <f>B309/B316</f>
         <v/>
       </c>
@@ -5808,18 +5819,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B318" s="14">
+      <c r="B318" s="15">
         <f>B315/B316</f>
         <v/>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="15" t="inlineStr">
+      <c r="A319" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B319" s="16">
+      <c r="B319" s="17">
         <f>(B312+B314)/B316</f>
         <v/>
       </c>
@@ -5834,22 +5845,22 @@
     <row r="321"/>
     <row r="322"/>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>Taringa warehouse EV chargers</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="12" t="inlineStr">
+      <c r="A324" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr"/>
-      <c r="B325" s="7" t="inlineStr">
+      <c r="A325" s="7" t="inlineStr"/>
+      <c r="B325" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5861,7 +5872,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B326" s="13" t="n">
+      <c r="B326" s="14" t="n">
         <v>42300</v>
       </c>
     </row>
@@ -5871,7 +5882,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B327" s="13" t="n">
+      <c r="B327" s="14" t="n">
         <v>-11900</v>
       </c>
     </row>
@@ -5881,7 +5892,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B328" s="13" t="n">
+      <c r="B328" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5891,7 +5902,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B329" s="17" t="n">
+      <c r="B329" s="18" t="n">
         <v>156</v>
       </c>
     </row>
@@ -5901,7 +5912,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B330" s="13" t="n">
+      <c r="B330" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5911,7 +5922,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B331" s="13">
+      <c r="B331" s="14">
         <f>-B329*B330</f>
         <v/>
       </c>
@@ -5922,18 +5933,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B332" s="13">
+      <c r="B332" s="14">
         <f>B326+B327+B328+B331</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="15" t="inlineStr">
+      <c r="A333" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B333" s="16">
+      <c r="B333" s="17">
         <f>B332/B326</f>
         <v/>
       </c>
@@ -5941,22 +5952,22 @@
     <row r="334"/>
     <row r="335"/>
     <row r="336">
-      <c r="A336" s="5" t="inlineStr">
+      <c r="A336" s="6" t="inlineStr">
         <is>
           <t>Taringa clinic LED lighting</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="12" t="inlineStr">
+      <c r="A337" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="6" t="inlineStr"/>
-      <c r="B338" s="7" t="inlineStr">
+      <c r="A338" s="7" t="inlineStr"/>
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5968,7 +5979,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B339" s="13" t="n">
+      <c r="B339" s="14" t="n">
         <v>41800</v>
       </c>
     </row>
@@ -5978,7 +5989,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B340" s="13" t="n">
+      <c r="B340" s="14" t="n">
         <v>-14500</v>
       </c>
     </row>
@@ -5988,7 +5999,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B341" s="13" t="n">
+      <c r="B341" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5998,7 +6009,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B342" s="17" t="n">
+      <c r="B342" s="18" t="n">
         <v>155</v>
       </c>
     </row>
@@ -6008,7 +6019,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B343" s="13" t="n">
+      <c r="B343" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6018,7 +6029,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B344" s="13">
+      <c r="B344" s="14">
         <f>-B342*B343</f>
         <v/>
       </c>
@@ -6029,18 +6040,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B345" s="13">
+      <c r="B345" s="14">
         <f>B339+B340+B341+B344</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="15" t="inlineStr">
+      <c r="A346" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B346" s="16">
+      <c r="B346" s="17">
         <f>B345/B339</f>
         <v/>
       </c>
@@ -6048,22 +6059,22 @@
     <row r="347"/>
     <row r="348"/>
     <row r="349">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>Kedron shop switchboard upgrade</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="12" t="inlineStr">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="6" t="inlineStr"/>
-      <c r="B351" s="7" t="inlineStr">
+      <c r="A351" s="7" t="inlineStr"/>
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6075,7 +6086,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B352" s="13" t="n">
+      <c r="B352" s="14" t="n">
         <v>40400</v>
       </c>
     </row>
@@ -6085,7 +6096,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
+      <c r="B353" s="14" t="n">
         <v>-14300</v>
       </c>
     </row>
@@ -6095,7 +6106,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B354" s="13" t="n">
+      <c r="B354" s="14" t="n">
         <v>-3600</v>
       </c>
     </row>
@@ -6105,7 +6116,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B355" s="17" t="n">
+      <c r="B355" s="18" t="n">
         <v>139.5</v>
       </c>
     </row>
@@ -6115,7 +6126,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B356" s="13" t="n">
+      <c r="B356" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6125,7 +6136,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B357" s="13">
+      <c r="B357" s="14">
         <f>-B355*B356</f>
         <v/>
       </c>
@@ -6136,18 +6147,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B358" s="13">
+      <c r="B358" s="14">
         <f>B352+B353+B354+B357</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="15" t="inlineStr">
+      <c r="A359" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B359" s="16">
+      <c r="B359" s="17">
         <f>B358/B352</f>
         <v/>
       </c>
@@ -6155,22 +6166,22 @@
     <row r="360"/>
     <row r="361"/>
     <row r="362">
-      <c r="A362" s="5" t="inlineStr">
+      <c r="A362" s="6" t="inlineStr">
         <is>
           <t>Salisbury gym air-con install</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="12" t="inlineStr">
+      <c r="A363" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="6" t="inlineStr"/>
-      <c r="B364" s="7" t="inlineStr">
+      <c r="A364" s="7" t="inlineStr"/>
+      <c r="B364" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6182,7 +6193,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B365" s="13" t="n">
+      <c r="B365" s="14" t="n">
         <v>20300</v>
       </c>
     </row>
@@ -6192,7 +6203,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B366" s="13" t="n">
+      <c r="B366" s="14" t="n">
         <v>-7800</v>
       </c>
     </row>
@@ -6202,7 +6213,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
+      <c r="B367" s="14" t="n">
         <v>-1300</v>
       </c>
     </row>
@@ -6212,7 +6223,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B368" s="17" t="n">
+      <c r="B368" s="18" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -6222,7 +6233,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B369" s="13" t="n">
+      <c r="B369" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6232,7 +6243,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B370" s="13">
+      <c r="B370" s="14">
         <f>-B368*B369</f>
         <v/>
       </c>
@@ -6243,18 +6254,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B371" s="13">
+      <c r="B371" s="14">
         <f>B365+B366+B367+B370</f>
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="15" t="inlineStr">
+      <c r="A372" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B372" s="16">
+      <c r="B372" s="17">
         <f>B371/B365</f>
         <v/>
       </c>
@@ -6262,27 +6273,27 @@
     <row r="373"/>
     <row r="374"/>
     <row r="375">
-      <c r="A375" s="5" t="inlineStr">
+      <c r="A375" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="12" t="inlineStr">
+      <c r="A376" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="6" t="inlineStr"/>
-      <c r="B377" s="7" t="inlineStr">
+      <c r="A377" s="7" t="inlineStr"/>
+      <c r="B377" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C377" s="7" t="inlineStr">
+      <c r="C377" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -6294,10 +6305,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B378" s="13" t="n">
+      <c r="B378" s="14" t="n">
         <v>32108</v>
       </c>
-      <c r="C378" s="13" t="n">
+      <c r="C378" s="14" t="n">
         <v>34106</v>
       </c>
     </row>
@@ -6307,10 +6318,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B379" s="13" t="n">
+      <c r="B379" s="14" t="n">
         <v>16608</v>
       </c>
-      <c r="C379" s="13" t="n">
+      <c r="C379" s="14" t="n">
         <v>17858</v>
       </c>
     </row>
@@ -6320,26 +6331,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B380" s="13">
+      <c r="B380" s="14">
         <f>B378-B379</f>
         <v/>
       </c>
-      <c r="C380" s="13">
+      <c r="C380" s="14">
         <f>C378-C379</f>
         <v/>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="15" t="inlineStr">
+      <c r="A381" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B381" s="16">
+      <c r="B381" s="17">
         <f>B380/B378</f>
         <v/>
       </c>
-      <c r="C381" s="16">
+      <c r="C381" s="17">
         <f>C380/C378</f>
         <v/>
       </c>
@@ -6347,27 +6358,27 @@
     <row r="382"/>
     <row r="383"/>
     <row r="384">
-      <c r="A384" s="5" t="inlineStr">
+      <c r="A384" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, February and January</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="12" t="inlineStr">
+      <c r="A385" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="6" t="inlineStr"/>
-      <c r="B386" s="7" t="inlineStr">
+      <c r="A386" s="7" t="inlineStr"/>
+      <c r="B386" s="8" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C386" s="7" t="inlineStr">
+      <c r="C386" s="8" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
@@ -6379,10 +6390,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B387" s="13" t="n">
+      <c r="B387" s="14" t="n">
         <v>32108</v>
       </c>
-      <c r="C387" s="13" t="n">
+      <c r="C387" s="14" t="n">
         <v>34106</v>
       </c>
     </row>
@@ -6392,10 +6403,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B388" s="13" t="n">
+      <c r="B388" s="14" t="n">
         <v>16608</v>
       </c>
-      <c r="C388" s="13" t="n">
+      <c r="C388" s="14" t="n">
         <v>17858</v>
       </c>
     </row>
@@ -6405,26 +6416,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B389" s="13">
+      <c r="B389" s="14">
         <f>B387-B388</f>
         <v/>
       </c>
-      <c r="C389" s="13">
+      <c r="C389" s="14">
         <f>C387-C388</f>
         <v/>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="15" t="inlineStr">
+      <c r="A390" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B390" s="16">
+      <c r="B390" s="17">
         <f>B389/B387</f>
         <v/>
       </c>
-      <c r="C390" s="16">
+      <c r="C390" s="17">
         <f>C389/C387</f>
         <v/>
       </c>
@@ -6432,22 +6443,22 @@
     <row r="391"/>
     <row r="392"/>
     <row r="393">
-      <c r="A393" s="5" t="inlineStr">
+      <c r="A393" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, February 2026</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="12" t="inlineStr">
+      <c r="A394" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="6" t="inlineStr"/>
-      <c r="B395" s="7" t="inlineStr">
+      <c r="A395" s="7" t="inlineStr"/>
+      <c r="B395" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -6459,7 +6470,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B396" s="13" t="n">
+      <c r="B396" s="14" t="n">
         <v>98246</v>
       </c>
     </row>
@@ -6469,7 +6480,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B397" s="13" t="n">
+      <c r="B397" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -6479,7 +6490,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B398" s="13" t="n">
+      <c r="B398" s="14" t="n">
         <v>59432</v>
       </c>
     </row>
@@ -6489,7 +6500,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B399" s="13">
+      <c r="B399" s="14">
         <f>B397-B398</f>
         <v/>
       </c>
@@ -6500,7 +6511,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B400" s="13">
+      <c r="B400" s="14">
         <f>B396-B399</f>
         <v/>
       </c>
@@ -6511,7 +6522,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B401" s="13" t="n">
+      <c r="B401" s="14" t="n">
         <v>59320</v>
       </c>
     </row>
@@ -6521,7 +6532,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B402" s="13">
+      <c r="B402" s="14">
         <f>B400-B401</f>
         <v/>
       </c>
@@ -6532,7 +6543,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B403" s="13" t="n">
+      <c r="B403" s="14" t="n">
         <v>218908</v>
       </c>
     </row>
@@ -6542,7 +6553,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B404" s="14">
+      <c r="B404" s="15">
         <f>B396/B403</f>
         <v/>
       </c>
@@ -6553,18 +6564,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B405" s="14">
+      <c r="B405" s="15">
         <f>B402/B403</f>
         <v/>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="15" t="inlineStr">
+      <c r="A406" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B406" s="16">
+      <c r="B406" s="17">
         <f>(B399+B401)/B403</f>
         <v/>
       </c>
@@ -6579,22 +6590,22 @@
     <row r="408"/>
     <row r="409"/>
     <row r="410">
-      <c r="A410" s="5" t="inlineStr">
+      <c r="A410" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, February</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="12" t="inlineStr">
+      <c r="A411" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="6" t="inlineStr"/>
-      <c r="B412" s="7" t="inlineStr">
+      <c r="A412" s="7" t="inlineStr"/>
+      <c r="B412" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -6606,7 +6617,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B413" s="13" t="n">
+      <c r="B413" s="14" t="n">
         <v>22982</v>
       </c>
     </row>
@@ -6616,7 +6627,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B414" s="13" t="n">
+      <c r="B414" s="14" t="n">
         <v>7020</v>
       </c>
     </row>
@@ -6626,7 +6637,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B415" s="14" t="n">
+      <c r="B415" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6636,7 +6647,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B416" s="13">
+      <c r="B416" s="14">
         <f>B414*(1+B415)</f>
         <v/>
       </c>
@@ -6647,7 +6658,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B417" s="13" t="n">
+      <c r="B417" s="14" t="n">
         <v>9126</v>
       </c>
     </row>
@@ -6657,18 +6668,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B418" s="13">
+      <c r="B418" s="14">
         <f>B413+B417</f>
         <v/>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="15" t="inlineStr">
+      <c r="A419" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B419" s="16">
+      <c r="B419" s="17">
         <f>B413/B418</f>
         <v/>
       </c>
@@ -6676,22 +6687,22 @@
     <row r="420"/>
     <row r="421"/>
     <row r="422">
-      <c r="A422" s="5" t="inlineStr">
+      <c r="A422" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, February</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="12" t="inlineStr">
+      <c r="A423" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="6" t="inlineStr"/>
-      <c r="B424" s="7" t="inlineStr">
+      <c r="A424" s="7" t="inlineStr"/>
+      <c r="B424" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -6703,7 +6714,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B425" s="13" t="n">
+      <c r="B425" s="14" t="n">
         <v>22982</v>
       </c>
     </row>
@@ -6713,7 +6724,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B426" s="13" t="n">
+      <c r="B426" s="14" t="n">
         <v>7020</v>
       </c>
     </row>
@@ -6723,7 +6734,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B427" s="14" t="n">
+      <c r="B427" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6733,7 +6744,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B428" s="13">
+      <c r="B428" s="14">
         <f>B426*(1+B427)</f>
         <v/>
       </c>
@@ -6744,7 +6755,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B429" s="13" t="n">
+      <c r="B429" s="14" t="n">
         <v>9126</v>
       </c>
     </row>
@@ -6754,18 +6765,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B430" s="13">
+      <c r="B430" s="14">
         <f>B425+B429</f>
         <v/>
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="15" t="inlineStr">
+      <c r="A431" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B431" s="16">
+      <c r="B431" s="17">
         <f>B425/B430</f>
         <v/>
       </c>
@@ -6773,22 +6784,22 @@
     <row r="432"/>
     <row r="433"/>
     <row r="434">
-      <c r="A434" s="5" t="inlineStr">
+      <c r="A434" s="6" t="inlineStr">
         <is>
           <t>1-hour call-outs (6)</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="12" t="inlineStr">
+      <c r="A435" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="6" t="inlineStr"/>
-      <c r="B436" s="7" t="inlineStr">
+      <c r="A436" s="7" t="inlineStr"/>
+      <c r="B436" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -6800,7 +6811,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B437" s="13" t="n">
+      <c r="B437" s="14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6810,7 +6821,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B438" s="13" t="n">
+      <c r="B438" s="14" t="n">
         <v>978</v>
       </c>
     </row>
@@ -6820,7 +6831,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B439" s="13" t="n">
+      <c r="B439" s="14" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -6830,7 +6841,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B440" s="13">
+      <c r="B440" s="14">
         <f>B438+B439</f>
         <v/>
       </c>
@@ -6841,7 +6852,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B441" s="13" t="n">
+      <c r="B441" s="14" t="n">
         <v>-770</v>
       </c>
     </row>
@@ -6851,7 +6862,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B442" s="13" t="n">
+      <c r="B442" s="14" t="n">
         <v>-408</v>
       </c>
     </row>
@@ -6861,18 +6872,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B443" s="13">
+      <c r="B443" s="14">
         <f>B440+B441+B442</f>
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="15" t="inlineStr">
+      <c r="A444" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B444" s="16">
+      <c r="B444" s="17">
         <f>B443/B440</f>
         <v/>
       </c>
@@ -6880,22 +6891,22 @@
     <row r="445"/>
     <row r="446"/>
     <row r="447">
-      <c r="A447" s="5" t="inlineStr">
+      <c r="A447" s="6" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (6)</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="12" t="inlineStr">
+      <c r="A448" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="6" t="inlineStr"/>
-      <c r="B449" s="7" t="inlineStr">
+      <c r="A449" s="7" t="inlineStr"/>
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -6907,7 +6918,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B450" s="13" t="n">
+      <c r="B450" s="14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6917,7 +6928,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B451" s="13" t="n">
+      <c r="B451" s="14" t="n">
         <v>1466</v>
       </c>
     </row>
@@ -6927,7 +6938,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B452" s="13" t="n">
+      <c r="B452" s="14" t="n">
         <v>1248</v>
       </c>
     </row>
@@ -6937,7 +6948,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B453" s="13">
+      <c r="B453" s="14">
         <f>B451+B452</f>
         <v/>
       </c>
@@ -6948,7 +6959,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B454" s="13" t="n">
+      <c r="B454" s="14" t="n">
         <v>-960</v>
       </c>
     </row>
@@ -6958,7 +6969,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B455" s="13" t="n">
+      <c r="B455" s="14" t="n">
         <v>-612</v>
       </c>
     </row>
@@ -6968,18 +6979,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B456" s="13">
+      <c r="B456" s="14">
         <f>B453+B454+B455</f>
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="15" t="inlineStr">
+      <c r="A457" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B457" s="16">
+      <c r="B457" s="17">
         <f>B456/B453</f>
         <v/>
       </c>
@@ -6987,22 +6998,22 @@
     <row r="458"/>
     <row r="459"/>
     <row r="460">
-      <c r="A460" s="5" t="inlineStr">
+      <c r="A460" s="6" t="inlineStr">
         <is>
           <t>2-hour call-outs (15)</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="12" t="inlineStr">
+      <c r="A461" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="6" t="inlineStr"/>
-      <c r="B462" s="7" t="inlineStr">
+      <c r="A462" s="7" t="inlineStr"/>
+      <c r="B462" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -7014,7 +7025,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B463" s="13" t="n">
+      <c r="B463" s="14" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7024,7 +7035,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B464" s="13" t="n">
+      <c r="B464" s="14" t="n">
         <v>4890</v>
       </c>
     </row>
@@ -7034,7 +7045,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B465" s="13" t="n">
+      <c r="B465" s="14" t="n">
         <v>2834</v>
       </c>
     </row>
@@ -7044,7 +7055,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B466" s="13">
+      <c r="B466" s="14">
         <f>B464+B465</f>
         <v/>
       </c>
@@ -7055,7 +7066,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B467" s="13" t="n">
+      <c r="B467" s="14" t="n">
         <v>-2180</v>
       </c>
     </row>
@@ -7065,7 +7076,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B468" s="13" t="n">
+      <c r="B468" s="14" t="n">
         <v>-2040</v>
       </c>
     </row>
@@ -7075,18 +7086,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B469" s="13">
+      <c r="B469" s="14">
         <f>B466+B467+B468</f>
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="15" t="inlineStr">
+      <c r="A470" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B470" s="16">
+      <c r="B470" s="17">
         <f>B469/B466</f>
         <v/>
       </c>
@@ -7094,22 +7105,22 @@
     <row r="471"/>
     <row r="472"/>
     <row r="473">
-      <c r="A473" s="5" t="inlineStr">
+      <c r="A473" s="6" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (4)</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="12" t="inlineStr">
+      <c r="A474" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="6" t="inlineStr"/>
-      <c r="B475" s="7" t="inlineStr">
+      <c r="A475" s="7" t="inlineStr"/>
+      <c r="B475" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -7121,7 +7132,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B476" s="13" t="n">
+      <c r="B476" s="14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7131,7 +7142,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B477" s="13" t="n">
+      <c r="B477" s="14" t="n">
         <v>1630</v>
       </c>
     </row>
@@ -7141,7 +7152,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B478" s="13" t="n">
+      <c r="B478" s="14" t="n">
         <v>598</v>
       </c>
     </row>
@@ -7151,7 +7162,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B479" s="13">
+      <c r="B479" s="14">
         <f>B477+B478</f>
         <v/>
       </c>
@@ -7162,7 +7173,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B480" s="13" t="n">
+      <c r="B480" s="14" t="n">
         <v>-460</v>
       </c>
     </row>
@@ -7172,7 +7183,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B481" s="13" t="n">
+      <c r="B481" s="14" t="n">
         <v>-680</v>
       </c>
     </row>
@@ -7182,18 +7193,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B482" s="13">
+      <c r="B482" s="14">
         <f>B479+B480+B481</f>
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="15" t="inlineStr">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B483" s="16">
+      <c r="B483" s="17">
         <f>B482/B479</f>
         <v/>
       </c>
@@ -7201,22 +7212,22 @@
     <row r="484"/>
     <row r="485"/>
     <row r="486">
-      <c r="A486" s="5" t="inlineStr">
+      <c r="A486" s="6" t="inlineStr">
         <is>
           <t>3-hour call-outs (18)</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="12" t="inlineStr">
+      <c r="A487" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="6" t="inlineStr"/>
-      <c r="B488" s="7" t="inlineStr">
+      <c r="A488" s="7" t="inlineStr"/>
+      <c r="B488" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -7228,7 +7239,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B489" s="13" t="n">
+      <c r="B489" s="14" t="n">
         <v>18</v>
       </c>
     </row>
@@ -7238,7 +7249,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B490" s="13" t="n">
+      <c r="B490" s="14" t="n">
         <v>8802</v>
       </c>
     </row>
@@ -7248,7 +7259,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B491" s="13" t="n">
+      <c r="B491" s="14" t="n">
         <v>2457</v>
       </c>
     </row>
@@ -7258,7 +7269,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B492" s="13">
+      <c r="B492" s="14">
         <f>B490+B491</f>
         <v/>
       </c>
@@ -7269,7 +7280,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B493" s="13" t="n">
+      <c r="B493" s="14" t="n">
         <v>-1890</v>
       </c>
     </row>
@@ -7279,7 +7290,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B494" s="13" t="n">
+      <c r="B494" s="14" t="n">
         <v>-3672</v>
       </c>
     </row>
@@ -7289,18 +7300,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B495" s="13">
+      <c r="B495" s="14">
         <f>B492+B493+B494</f>
         <v/>
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="15" t="inlineStr">
+      <c r="A496" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B496" s="16">
+      <c r="B496" s="17">
         <f>B495/B492</f>
         <v/>
       </c>
@@ -7308,22 +7319,22 @@
     <row r="497"/>
     <row r="498"/>
     <row r="499">
-      <c r="A499" s="5" t="inlineStr">
+      <c r="A499" s="6" t="inlineStr">
         <is>
           <t>4-hour call-outs (8)</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="12" t="inlineStr">
+      <c r="A500" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in February, added together</t>
         </is>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="6" t="inlineStr"/>
-      <c r="B501" s="7" t="inlineStr">
+      <c r="A501" s="7" t="inlineStr"/>
+      <c r="B501" s="8" t="inlineStr">
         <is>
           <t>Feb 2026</t>
         </is>
@@ -7335,7 +7346,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B502" s="13" t="n">
+      <c r="B502" s="14" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7345,7 +7356,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B503" s="13" t="n">
+      <c r="B503" s="14" t="n">
         <v>5216</v>
       </c>
     </row>
@@ -7355,7 +7366,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B504" s="13" t="n">
+      <c r="B504" s="14" t="n">
         <v>988</v>
       </c>
     </row>
@@ -7365,7 +7376,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B505" s="13">
+      <c r="B505" s="14">
         <f>B503+B504</f>
         <v/>
       </c>
@@ -7376,7 +7387,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B506" s="13" t="n">
+      <c r="B506" s="14" t="n">
         <v>-760</v>
       </c>
     </row>
@@ -7386,7 +7397,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B507" s="13" t="n">
+      <c r="B507" s="14" t="n">
         <v>-2176</v>
       </c>
     </row>
@@ -7396,18 +7407,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B508" s="13">
+      <c r="B508" s="14">
         <f>B505+B506+B507</f>
         <v/>
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="15" t="inlineStr">
+      <c r="A509" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B509" s="16">
+      <c r="B509" s="17">
         <f>B508/B505</f>
         <v/>
       </c>
@@ -7421,7 +7432,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7699,2152 +7710,2152 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: February 2026 · Data status: Jan 2026 locked · Feb 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>191014</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>114334</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="15">
         <f>IF(D6=0,"",F6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>200124</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>113016</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <f>IF(D7=0,"",F7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>159406</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>85316</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f>IF(D8=0,"",F8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>156794</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>80742</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <f>IF(D9=0,"",F9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>179190</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>102348</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <f>IF(D10=0,"",F10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>150465</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>85752</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <f>IF(D11=0,"",F11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>138865</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>76808</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f>IF(D12=0,"",F12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>144649</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>83700</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <f>IF(D13=0,"",F13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>183265</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>97584</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <f>IF(D14=0,"",F14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>208588</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>120326</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <f>IF(D15=0,"",F15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>155118</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>78258</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f>IF(D16=0,"",F16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>143077</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>80054</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <f>IF(D17=0,"",F17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <f>IF(D18=0,"",F18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>194966</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>115942</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>IF(D19=0,"",F19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>150283</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>84626</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <f>IF(D20=0,"",F20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>183306</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>106590</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <f>IF(D21=0,"",F21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>218908</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>120662</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f>IF(D22=0,"",F22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <f>IF(D23=0,"",F23/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <f>IF(D24=0,"",F24/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>IF(D25=0,"",F25/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="15">
         <f>IF(D26=0,"",F26/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <f>IF(D27=0,"",F27/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f>IF(D28=0,"",F28/D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f>IF(D29=0,"",F29/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="15">
         <f>IF(D30=0,"",F30/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>35720</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <f>IF(D31=0,"",F31/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="15">
         <f>IF(D32=0,"",F32/D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="15">
         <f>IF(D33=0,"",F33/D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="15">
         <f>IF(D34=0,"",F34/D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="15">
         <f>IF(D35=0,"",F35/D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="15">
         <f>IF(D36=0,"",F36/D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <f>IF(D37=0,"",F37/D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="15">
         <f>IF(D38=0,"",F38/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <f>IF(D39=0,"",F39/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>141600</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>92430</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <f>IF(D40=0,"",F40/D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>147100</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>89070</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <f>IF(D41=0,"",F41/D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="14" t="n">
         <v>103700</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="14" t="n">
         <v>59908</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <f>IF(D42=0,"",F42/D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="14" t="n">
         <v>100100</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="14" t="n">
         <v>54678</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <f>IF(D43=0,"",F43/D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="14" t="n">
         <v>118600</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="14" t="n">
         <v>74966</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <f>IF(D44=0,"",F44/D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="14" t="n">
         <v>96400</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="14" t="n">
         <v>61664</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <f>IF(D45=0,"",F45/D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="14" t="n">
         <v>83900</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="14" t="n">
         <v>52264</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="15">
         <f>IF(D46=0,"",F46/D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="14" t="n">
         <v>89900</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="14" t="n">
         <v>59534</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="15">
         <f>IF(D47=0,"",F47/D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="14" t="n">
         <v>126300</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <v>72976</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="15">
         <f>IF(D48=0,"",F48/D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="14" t="n">
         <v>152100</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="14" t="n">
         <v>96920</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="15">
         <f>IF(D49=0,"",F49/D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="14" t="n">
         <v>96500</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="14" t="n">
         <v>53590</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f>IF(D50=0,"",F50/D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="14" t="n">
         <v>84200</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="14" t="n">
         <v>55440</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="15">
         <f>IF(D51=0,"",F51/D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="15">
         <f>IF(D52=0,"",F52/D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="14" t="n">
         <v>126900</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="14" t="n">
         <v>87174</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="15">
         <f>IF(D53=0,"",F53/D53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="14" t="n">
         <v>78100</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="14" t="n">
         <v>53408</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f>IF(D54=0,"",F54/D54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="14" t="n">
         <v>109100</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="14" t="n">
         <v>74216</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="15">
         <f>IF(D55=0,"",F55/D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="14" t="n">
         <v>144800</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="14" t="n">
         <v>88896</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="15">
         <f>IF(D56=0,"",F56/D56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="14" t="n">
         <v>21764</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="14" t="n">
         <v>11484</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="15">
         <f>IF(D57=0,"",F57/D57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="14" t="n">
         <v>25374</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E58" s="14" t="n">
         <v>13526</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <f>D58-E58</f>
         <v/>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="15">
         <f>IF(D58=0,"",F58/D58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="14" t="n">
         <v>28056</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="14" t="n">
         <v>14988</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <f>D59-E59</f>
         <v/>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="15">
         <f>IF(D59=0,"",F59/D59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="14" t="n">
         <v>29044</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="14" t="n">
         <v>15644</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <f>D60-E60</f>
         <v/>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="15">
         <f>IF(D60=0,"",F60/D60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="14" t="n">
         <v>29290</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="14">
         <f>D61-E61</f>
         <v/>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="15">
         <f>IF(D61=0,"",F61/D61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="14" t="n">
         <v>22765</v>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="14" t="n">
         <v>12306</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="14">
         <f>D62-E62</f>
         <v/>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="15">
         <f>IF(D62=0,"",F62/D62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="14" t="n">
         <v>23665</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="14" t="n">
         <v>12762</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="14">
         <f>D63-E63</f>
         <v/>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="15">
         <f>IF(D63=0,"",F63/D63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="14" t="n">
         <v>23449</v>
       </c>
-      <c r="E64" s="13" t="n">
+      <c r="E64" s="14" t="n">
         <v>12384</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="14">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="14">
+      <c r="G64" s="15">
         <f>IF(D64=0,"",F64/D64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="14" t="n">
         <v>21245</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="14" t="n">
         <v>11162</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="14">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="14">
+      <c r="G65" s="15">
         <f>IF(D65=0,"",F65/D65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="14" t="n">
         <v>19288</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="14" t="n">
         <v>9960</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="14">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="14">
+      <c r="G66" s="15">
         <f>IF(D66=0,"",F66/D66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="14" t="n">
         <v>21418</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="14" t="n">
         <v>11222</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="14">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="14">
+      <c r="G67" s="15">
         <f>IF(D67=0,"",F67/D67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="14" t="n">
         <v>21677</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="14" t="n">
         <v>11168</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="14">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="14">
+      <c r="G68" s="15">
         <f>IF(D68=0,"",F68/D68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="14">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="14">
+      <c r="G69" s="15">
         <f>IF(D69=0,"",F69/D69)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B70" s="18" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C70" s="18" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="14" t="n">
         <v>27966</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E70" s="14" t="n">
         <v>14252</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="14">
         <f>D70-E70</f>
         <v/>
       </c>
-      <c r="G70" s="14">
+      <c r="G70" s="15">
         <f>IF(D70=0,"",F70/D70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="14" t="n">
         <v>32083</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="14" t="n">
         <v>16702</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="14">
         <f>D71-E71</f>
         <v/>
       </c>
-      <c r="G71" s="14">
+      <c r="G71" s="15">
         <f>IF(D71=0,"",F71/D71)</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B72" s="18" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="14" t="n">
         <v>34106</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="14" t="n">
         <v>17858</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="14">
         <f>D72-E72</f>
         <v/>
       </c>
-      <c r="G72" s="14">
+      <c r="G72" s="15">
         <f>IF(D72=0,"",F72/D72)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="14" t="n">
         <v>32108</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="14" t="n">
         <v>16608</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="14">
         <f>D73-E73</f>
         <v/>
       </c>
-      <c r="G73" s="14">
+      <c r="G73" s="15">
         <f>IF(D73=0,"",F73/D73)</f>
         <v/>
       </c>
@@ -9855,7 +9866,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
